--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_11_40.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_11_40.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4277991.384125776</v>
+        <v>4237636.728922375</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6764066.245458388</v>
+        <v>6764066.24545834</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6764066.245458388</v>
+        <v>6764066.24545834</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3307259.142253736</v>
+        <v>3307259.142253665</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3307259.142253736</v>
+        <v>3307259.142253665</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49037313.29286492</v>
+        <v>49037313.29286493</v>
       </c>
     </row>
   </sheetData>
@@ -660,7 +660,7 @@
         <v>49.47457824299391</v>
       </c>
       <c r="D2" t="n">
-        <v>410.3391557398498</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E2" t="n">
         <v>4.363289606868648</v>
@@ -669,49 +669,49 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>3.75737228701621</v>
+        <v>403.7573722870162</v>
       </c>
       <c r="H2" t="n">
-        <v>8.009658703527407</v>
+        <v>408.0096587035274</v>
       </c>
       <c r="I2" t="n">
         <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
-        <v>782.5629999999998</v>
+        <v>419.7382696589336</v>
       </c>
       <c r="K2" t="n">
+        <v>66.13418277950457</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>708.2028517302315</v>
+      </c>
+      <c r="N2" t="n">
         <v>815</v>
       </c>
-      <c r="L2" t="n">
-        <v>305.1247975535859</v>
-      </c>
-      <c r="M2" t="n">
-        <v>298.9910820919849</v>
-      </c>
-      <c r="N2" t="n">
-        <v>195.5855355810472</v>
-      </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>798.7814999999999</v>
+        <v>371.9706110579117</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>94.84816780232291</v>
+        <v>494.8481678023229</v>
       </c>
       <c r="T2" t="n">
-        <v>586.6755817285639</v>
+        <v>283.1660146029995</v>
       </c>
       <c r="U2" t="n">
-        <v>596.5903282513405</v>
+        <v>249.2212965486107</v>
       </c>
       <c r="V2" t="n">
         <v>229.8510241668239</v>
@@ -720,7 +720,7 @@
         <v>238.3734759809475</v>
       </c>
       <c r="X2" t="n">
-        <v>592.2818334606677</v>
+        <v>192.2818334606677</v>
       </c>
       <c r="Y2" t="n">
         <v>111.3174326828064</v>
@@ -745,7 +745,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>68.12858063546007</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -790,10 +790,10 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2103597601867477</v>
+        <v>284.8567190531298</v>
       </c>
       <c r="V3" t="n">
-        <v>14.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W3" t="n">
         <v>32.37314290982852</v>
@@ -802,7 +802,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>399.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -900,10 +900,10 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E5" t="n">
-        <v>4.363289606868648</v>
+        <v>404.3632896068686</v>
       </c>
       <c r="F5" t="n">
-        <v>4.889628708011855</v>
+        <v>404.8896287080119</v>
       </c>
       <c r="G5" t="n">
         <v>3.75737228701621</v>
@@ -915,19 +915,19 @@
         <v>150.0811596826846</v>
       </c>
       <c r="J5" t="n">
-        <v>798.7814999999999</v>
+        <v>419.7382696589347</v>
       </c>
       <c r="K5" t="n">
-        <v>798.7814999999998</v>
+        <v>815</v>
       </c>
       <c r="L5" t="n">
-        <v>731.9356864956214</v>
+        <v>783.0093003026253</v>
       </c>
       <c r="M5" t="n">
         <v>298.9910820919849</v>
       </c>
       <c r="N5" t="n">
-        <v>195.5855355810484</v>
+        <v>507.3366521151469</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -945,22 +945,22 @@
         <v>94.84816780232291</v>
       </c>
       <c r="T5" t="n">
-        <v>186.6755817285639</v>
+        <v>586.6755817285639</v>
       </c>
       <c r="U5" t="n">
-        <v>649.2212965486107</v>
+        <v>596.5903282513409</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
       </c>
       <c r="W5" t="n">
-        <v>638.3734759809475</v>
+        <v>238.3734759809475</v>
       </c>
       <c r="X5" t="n">
-        <v>539.6508651633975</v>
+        <v>192.2818334606677</v>
       </c>
       <c r="Y5" t="n">
-        <v>511.3174326828064</v>
+        <v>111.3174326828064</v>
       </c>
     </row>
     <row r="6">
@@ -970,16 +970,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>167.1158402638074</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>148.6880250402008</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1131,16 +1131,16 @@
         <v>481.9993129555745</v>
       </c>
       <c r="C8" t="n">
-        <v>146.9247696284082</v>
+        <v>449.4745782429939</v>
       </c>
       <c r="D8" t="n">
         <v>10.33915573984979</v>
       </c>
       <c r="E8" t="n">
-        <v>4.363289606868648</v>
+        <v>404.3632896068686</v>
       </c>
       <c r="F8" t="n">
-        <v>4.889628708011855</v>
+        <v>404.8896287080119</v>
       </c>
       <c r="G8" t="n">
         <v>3.75737228701621</v>
@@ -1152,25 +1152,25 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>798.7814999999999</v>
+        <v>419.7382696589336</v>
       </c>
       <c r="K8" t="n">
-        <v>767.4274152265731</v>
+        <v>815</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>783.0093003026029</v>
       </c>
       <c r="M8" t="n">
         <v>298.9910820919849</v>
       </c>
       <c r="N8" t="n">
-        <v>815</v>
+        <v>195.5855355810472</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>143.8753068501041</v>
+        <v>311.7511165340999</v>
       </c>
       <c r="Q8" t="n">
         <v>371.9706110579117</v>
@@ -1179,16 +1179,16 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>94.84816780232291</v>
+        <v>192.2983591877375</v>
       </c>
       <c r="T8" t="n">
         <v>186.6755817285639</v>
       </c>
       <c r="U8" t="n">
-        <v>649.2212965486107</v>
+        <v>249.2212965486107</v>
       </c>
       <c r="V8" t="n">
-        <v>629.8510241668239</v>
+        <v>229.8510241668239</v>
       </c>
       <c r="W8" t="n">
         <v>238.3734759809475</v>
@@ -1197,7 +1197,7 @@
         <v>192.2818334606677</v>
       </c>
       <c r="Y8" t="n">
-        <v>511.3174326828064</v>
+        <v>111.3174326828064</v>
       </c>
     </row>
     <row r="9">
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1255,10 +1255,10 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>387.8730357844536</v>
+        <v>204.9994216758019</v>
       </c>
       <c r="S9" t="n">
-        <v>66.5639999646113</v>
+        <v>466.5639999646113</v>
       </c>
       <c r="T9" t="n">
         <v>5.357765217513816</v>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>256.9993129555745</v>
       </c>
       <c r="C11" t="n">
-        <v>152.7832802660231</v>
+        <v>224.4745782429939</v>
       </c>
       <c r="D11" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>179.3632896068686</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G11" t="n">
         <v>178.7573722870162</v>
       </c>
       <c r="H11" t="n">
-        <v>183.0096587035274</v>
+        <v>14.14170354910814</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1416,13 +1416,13 @@
         <v>25.87859882829446</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>269.8481678023229</v>
       </c>
       <c r="T11" t="n">
         <v>361.6755817285639</v>
       </c>
       <c r="U11" t="n">
-        <v>424.2212965486107</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>404.8510241668239</v>
@@ -1532,7 +1532,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>55.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1568,10 +1568,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>342.1496093272374</v>
       </c>
       <c r="R13" t="n">
-        <v>227.474477742437</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>62.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1623,7 +1623,7 @@
         <v>129.0096587035274</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>3.450191385413969</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1650,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.450191385414405</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>215.8481678023229</v>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8.113800337078658</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -1787,16 +1787,16 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>9.520773801143037</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>13.63367669541927</v>
       </c>
       <c r="M16" t="n">
-        <v>20.35376554145563</v>
+        <v>241.6316114025499</v>
       </c>
       <c r="N16" t="n">
-        <v>292.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -1811,7 +1811,7 @@
         <v>447.6021279811511</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>83.37347970285543</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1829,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>8.465352849462363</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1854,13 +1854,13 @@
         <v>125.8896287080119</v>
       </c>
       <c r="G17" t="n">
-        <v>124.7573722870162</v>
+        <v>128.2075636724302</v>
       </c>
       <c r="H17" t="n">
         <v>129.0096587035274</v>
       </c>
       <c r="I17" t="n">
-        <v>3.450191385413969</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2003,7 +2003,7 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>361.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>326.4202810950877</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>255.2652880979692</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S19" t="n">
         <v>83.37347970285543</v>
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.465352849462363</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2234,16 +2234,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>8.113800337078658</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>6.53621805555548</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1.98090483695654</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -2261,25 +2261,25 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>9.520773801143037</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>144.5476281577792</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>241.6316114025499</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>292.1850752716849</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>73.25953106976577</v>
       </c>
       <c r="P22" t="n">
-        <v>408.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>369.327645604236</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
         <v>129.0096587035274</v>
       </c>
       <c r="I23" t="n">
-        <v>3.450191385413969</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.450191385414405</v>
       </c>
       <c r="S23" t="n">
         <v>215.8481678023229</v>
@@ -2498,16 +2498,16 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>9.520773801143037</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>144.5476281577792</v>
       </c>
       <c r="M25" t="n">
-        <v>37.93656963662772</v>
+        <v>241.6316114025499</v>
       </c>
       <c r="N25" t="n">
-        <v>292.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -2519,7 +2519,7 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>447.6021279811511</v>
+        <v>382.0237595279917</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2550,13 +2550,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>256.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>224.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>179.3632896068686</v>
@@ -2565,10 +2565,10 @@
         <v>179.8896287080119</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H26" t="n">
-        <v>62.30471823180212</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
         <v>269.8481678023229</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>139.6695409513339</v>
       </c>
       <c r="U26" t="n">
         <v>424.2212965486107</v>
@@ -2619,7 +2619,7 @@
         <v>367.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>286.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2726,7 +2726,7 @@
         <v>20.04387284153003</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2735,19 +2735,19 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>63.52077380114304</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>198.5476281577792</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>60.03733452678505</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>325.8768625873259</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -2790,13 +2790,13 @@
         <v>230.9993129555745</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>198.4745782429939</v>
       </c>
       <c r="D29" t="n">
         <v>159.3391557398498</v>
       </c>
       <c r="E29" t="n">
-        <v>153.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>153.8896287080119</v>
@@ -2838,7 +2838,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>129.2702814774122</v>
       </c>
       <c r="T29" t="n">
         <v>335.6755817285639</v>
@@ -2847,7 +2847,7 @@
         <v>398.2212965486107</v>
       </c>
       <c r="V29" t="n">
-        <v>292.9151615975553</v>
+        <v>378.8510241668239</v>
       </c>
       <c r="W29" t="n">
         <v>387.3734759809475</v>
@@ -2856,7 +2856,7 @@
         <v>341.2818334606677</v>
       </c>
       <c r="Y29" t="n">
-        <v>260.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2975,16 +2975,16 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
         <v>92.13264982743065</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
       </c>
       <c r="P31" t="n">
         <v>436.4478973282775</v>
@@ -3027,7 +3027,7 @@
         <v>193.9993129555745</v>
       </c>
       <c r="C32" t="n">
-        <v>161.4745782429939</v>
+        <v>151.2159696284084</v>
       </c>
       <c r="D32" t="n">
         <v>122.3391557398498</v>
@@ -3051,10 +3051,10 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>47.83862152373393</v>
       </c>
       <c r="L32" t="n">
-        <v>47.83862152370174</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3081,7 +3081,7 @@
         <v>298.6755817285639</v>
       </c>
       <c r="U32" t="n">
-        <v>350.9626879340248</v>
+        <v>361.2212965486107</v>
       </c>
       <c r="V32" t="n">
         <v>341.8510241668239</v>
@@ -3209,31 +3209,31 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>0.5207738011430365</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>135.5476281577792</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>232.6316114025499</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>86.65539425427258</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>399.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>420.1361585657629</v>
+        <v>438.6021279811511</v>
       </c>
       <c r="S34" t="n">
-        <v>74.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
         <v>161.4745782429939</v>
       </c>
       <c r="D35" t="n">
-        <v>112.0805471252643</v>
+        <v>122.3391557398498</v>
       </c>
       <c r="E35" t="n">
         <v>116.3632896068686</v>
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>47.83862152370034</v>
+        <v>47.83862152370594</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -3315,7 +3315,7 @@
         <v>206.8481678023229</v>
       </c>
       <c r="T35" t="n">
-        <v>298.6755817285639</v>
+        <v>288.4169731139784</v>
       </c>
       <c r="U35" t="n">
         <v>361.2212965486107</v>
@@ -3452,25 +3452,25 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>232.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>283.1850752716849</v>
       </c>
       <c r="O37" t="n">
-        <v>148.3503165103394</v>
+        <v>211.3245629969334</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>399.4478973282775</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>438.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>74.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3513,7 +3513,7 @@
         <v>116.8896287080119</v>
       </c>
       <c r="G38" t="n">
-        <v>115.7573722870074</v>
+        <v>115.7573722870162</v>
       </c>
       <c r="H38" t="n">
         <v>120.0096587035274</v>
@@ -3525,7 +3525,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>47.8386215239999</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -3537,7 +3537,7 @@
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>47.83862153588959</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -3549,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>206.8481678023229</v>
+        <v>196.5895591881019</v>
       </c>
       <c r="T38" t="n">
         <v>298.6755817285639</v>
@@ -3567,7 +3567,7 @@
         <v>304.2818334606677</v>
       </c>
       <c r="Y38" t="n">
-        <v>213.0588240682295</v>
+        <v>223.3174326828064</v>
       </c>
     </row>
     <row r="39">
@@ -3683,7 +3683,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0.5207738011430365</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -3698,13 +3698,13 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>381.2240156672993</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>437.839266425598</v>
+        <v>380.9819279128893</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>438.6021279811511</v>
       </c>
       <c r="S40" t="n">
         <v>74.37347970285543</v>
@@ -3741,7 +3741,7 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>215.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>208.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -3786,7 +3786,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>299.8481678023229</v>
+        <v>298.4232424760055</v>
       </c>
       <c r="T41" t="n">
         <v>391.6755817285639</v>
@@ -3798,13 +3798,13 @@
         <v>434.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>334.1694553105705</v>
+        <v>443.3734759809475</v>
       </c>
       <c r="X41" t="n">
         <v>397.2818334606677</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>316.3174326828064</v>
       </c>
     </row>
     <row r="42">
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>189.5565566463266</v>
       </c>
       <c r="C42" t="n">
         <v>166.0999124455193</v>
@@ -3823,10 +3823,10 @@
         <v>152.9376868977026</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>147.6720972219126</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>144.6362423378769</v>
       </c>
       <c r="G42" t="n">
         <v>130.7395358750273</v>
@@ -3862,10 +3862,10 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>352.2737972923793</v>
+        <v>235.3542456086117</v>
       </c>
       <c r="S42" t="n">
-        <v>271.5639999646113</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
         <v>210.3577652175138</v>
@@ -3877,7 +3877,7 @@
         <v>219.5106671915202</v>
       </c>
       <c r="W42" t="n">
-        <v>0.1251381725717442</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>224.8627394453875</v>
@@ -3929,7 +3929,7 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>137.5501316579666</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -3953,10 +3953,10 @@
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>4.170310216216194</v>
       </c>
       <c r="W43" t="n">
-        <v>31.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
         <v>0</v>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>366.9993129555745</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -3984,16 +3984,16 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>289.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>288.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>293.0096587035274</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>35.08115968268461</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,19 +4023,19 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>379.8481678023229</v>
+        <v>45.53199758136074</v>
       </c>
       <c r="T44" t="n">
-        <v>242.9547212866966</v>
+        <v>471.6755817285639</v>
       </c>
       <c r="U44" t="n">
-        <v>534.2212965486107</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
         <v>514.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>523.3734759809475</v>
       </c>
       <c r="X44" t="n">
         <v>477.2818334606677</v>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>269.5565566463266</v>
       </c>
       <c r="C45" t="n">
         <v>246.0999124455193</v>
@@ -4099,25 +4099,25 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>265.5255028074559</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>290.3577652175138</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>285.2103597601867</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>266.674331693442</v>
       </c>
       <c r="W45" t="n">
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>304.8627394453875</v>
       </c>
       <c r="Y45" t="n">
         <v>284.3913927661343</v>
@@ -4297,22 +4297,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>702.4877201726794</v>
+        <v>1106.528124213083</v>
       </c>
       <c r="C2" t="n">
-        <v>652.5133987151097</v>
+        <v>1056.553802755514</v>
       </c>
       <c r="D2" t="n">
-        <v>238.0294030182917</v>
+        <v>1046.1102110991</v>
       </c>
       <c r="E2" t="n">
-        <v>233.6220397790304</v>
+        <v>1041.702847859838</v>
       </c>
       <c r="F2" t="n">
-        <v>228.6830208820487</v>
+        <v>1036.763828962857</v>
       </c>
       <c r="G2" t="n">
-        <v>224.8876953396081</v>
+        <v>628.9280993800121</v>
       </c>
       <c r="H2" t="n">
         <v>216.7971309926107</v>
@@ -4321,52 +4321,52 @@
         <v>65.2</v>
       </c>
       <c r="J2" t="n">
-        <v>81.58232323232345</v>
+        <v>448.0719498394611</v>
       </c>
       <c r="K2" t="n">
-        <v>65.2</v>
+        <v>1156.448952311257</v>
       </c>
       <c r="L2" t="n">
-        <v>532.1723410838711</v>
+        <v>1963.298952311256</v>
       </c>
       <c r="M2" t="n">
-        <v>1037.011147051563</v>
+        <v>2054.792536422134</v>
       </c>
       <c r="N2" t="n">
-        <v>1646.3</v>
+        <v>2038.41021318981</v>
       </c>
       <c r="O2" t="n">
-        <v>2453.15</v>
+        <v>2022.027889957487</v>
       </c>
       <c r="P2" t="n">
-        <v>3260</v>
+        <v>2828.877889957487</v>
       </c>
       <c r="Q2" t="n">
         <v>3260</v>
       </c>
       <c r="R2" t="n">
-        <v>3260</v>
+        <v>3006.587273910814</v>
       </c>
       <c r="S2" t="n">
-        <v>3164.193769896644</v>
+        <v>2506.740639767053</v>
       </c>
       <c r="T2" t="n">
-        <v>2571.592172191024</v>
+        <v>2220.714362390286</v>
       </c>
       <c r="U2" t="n">
         <v>1968.975679007851</v>
       </c>
       <c r="V2" t="n">
-        <v>1736.802927324191</v>
+        <v>1736.80292732419</v>
       </c>
       <c r="W2" t="n">
         <v>1496.021638454547</v>
       </c>
       <c r="X2" t="n">
-        <v>897.757160211448</v>
+        <v>1301.797564251852</v>
       </c>
       <c r="Y2" t="n">
-        <v>785.3153090166941</v>
+        <v>1189.355713057098</v>
       </c>
     </row>
     <row r="3">
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>353.3363298250592</v>
+        <v>65.2</v>
       </c>
       <c r="C3" t="n">
-        <v>353.3363298250592</v>
+        <v>65.2</v>
       </c>
       <c r="D3" t="n">
-        <v>353.3363298250592</v>
+        <v>65.2</v>
       </c>
       <c r="E3" t="n">
-        <v>353.3363298250592</v>
+        <v>65.2</v>
       </c>
       <c r="F3" t="n">
-        <v>284.5195817084329</v>
+        <v>65.2</v>
       </c>
       <c r="G3" t="n">
-        <v>284.5195817084329</v>
+        <v>65.2</v>
       </c>
       <c r="H3" t="n">
-        <v>284.5195817084329</v>
+        <v>65.2</v>
       </c>
       <c r="I3" t="n">
         <v>65.2</v>
@@ -4433,19 +4433,19 @@
         <v>824.3952208079455</v>
       </c>
       <c r="U3" t="n">
-        <v>824.1827362016962</v>
+        <v>536.6611611583195</v>
       </c>
       <c r="V3" t="n">
-        <v>809.5254966143021</v>
+        <v>117.9635175305213</v>
       </c>
       <c r="W3" t="n">
-        <v>776.82535226094</v>
+        <v>85.26337317715914</v>
       </c>
       <c r="X3" t="n">
-        <v>756.7619790837808</v>
+        <v>65.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>353.3363298250592</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="4">
@@ -4455,31 +4455,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>638.2188222554639</v>
+        <v>1162.659747887578</v>
       </c>
       <c r="C4" t="n">
-        <v>638.2188222554639</v>
+        <v>1288.661753706013</v>
       </c>
       <c r="D4" t="n">
-        <v>638.2188222554639</v>
+        <v>1288.661753706013</v>
       </c>
       <c r="E4" t="n">
-        <v>756.047726466877</v>
+        <v>1406.490657917426</v>
       </c>
       <c r="F4" t="n">
-        <v>880.4086990588124</v>
+        <v>1406.490657917426</v>
       </c>
       <c r="G4" t="n">
-        <v>935.0424833281066</v>
+        <v>1406.490657917426</v>
       </c>
       <c r="H4" t="n">
-        <v>1104.559068487504</v>
+        <v>1576.007243076824</v>
       </c>
       <c r="I4" t="n">
-        <v>1104.559068487504</v>
+        <v>1576.007243076824</v>
       </c>
       <c r="J4" t="n">
-        <v>1465.642809139955</v>
+        <v>1576.007243076824</v>
       </c>
       <c r="K4" t="n">
         <v>1576.007243076824</v>
@@ -4509,22 +4509,22 @@
         <v>65.2</v>
       </c>
       <c r="T4" t="n">
-        <v>65.2</v>
+        <v>253.2756791588048</v>
       </c>
       <c r="U4" t="n">
-        <v>65.2</v>
+        <v>417.7500073724363</v>
       </c>
       <c r="V4" t="n">
-        <v>264.0213928859459</v>
+        <v>616.5714002583823</v>
       </c>
       <c r="W4" t="n">
-        <v>264.0213928859459</v>
+        <v>788.4623185180596</v>
       </c>
       <c r="X4" t="n">
-        <v>415.0521839101394</v>
+        <v>939.4931095422531</v>
       </c>
       <c r="Y4" t="n">
-        <v>526.4614845891717</v>
+        <v>1050.902410221285</v>
       </c>
     </row>
     <row r="5">
@@ -4534,16 +4534,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>298.4473161322752</v>
+        <v>1106.528124213083</v>
       </c>
       <c r="C5" t="n">
-        <v>248.4729946747056</v>
+        <v>1056.553802755514</v>
       </c>
       <c r="D5" t="n">
-        <v>238.0294030182917</v>
+        <v>1046.1102110991</v>
       </c>
       <c r="E5" t="n">
-        <v>233.6220397790304</v>
+        <v>637.6624438194344</v>
       </c>
       <c r="F5" t="n">
         <v>228.6830208820487</v>
@@ -4558,16 +4558,16 @@
         <v>65.2</v>
       </c>
       <c r="J5" t="n">
-        <v>65.2</v>
+        <v>448.0719498394611</v>
       </c>
       <c r="K5" t="n">
-        <v>65.2</v>
+        <v>431.6896266071377</v>
       </c>
       <c r="L5" t="n">
-        <v>101.0502310413578</v>
+        <v>415.9503487525697</v>
       </c>
       <c r="M5" t="n">
-        <v>605.8890370090498</v>
+        <v>920.7891547202616</v>
       </c>
       <c r="N5" t="n">
         <v>1215.177889957487</v>
@@ -4588,22 +4588,22 @@
         <v>3164.193769896644</v>
       </c>
       <c r="T5" t="n">
-        <v>2975.632576231427</v>
+        <v>2571.592172191024</v>
       </c>
       <c r="U5" t="n">
-        <v>2319.853488808588</v>
+        <v>1968.975679007851</v>
       </c>
       <c r="V5" t="n">
-        <v>2087.680737124928</v>
+        <v>1736.80292732419</v>
       </c>
       <c r="W5" t="n">
-        <v>1442.85904421488</v>
+        <v>1496.021638454547</v>
       </c>
       <c r="X5" t="n">
-        <v>897.7571602114479</v>
+        <v>1301.797564251852</v>
       </c>
       <c r="Y5" t="n">
-        <v>381.2749049762899</v>
+        <v>1189.355713057098</v>
       </c>
     </row>
     <row r="6">
@@ -4613,13 +4613,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>762.785640524864</v>
+        <v>931.5895195792149</v>
       </c>
       <c r="C6" t="n">
-        <v>762.785640524864</v>
+        <v>566.8421332706096</v>
       </c>
       <c r="D6" t="n">
-        <v>411.3334315372855</v>
+        <v>215.3899242830311</v>
       </c>
       <c r="E6" t="n">
         <v>65.2</v>
@@ -4692,25 +4692,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>924.0263740890871</v>
+        <v>911.2745562607827</v>
       </c>
       <c r="C7" t="n">
-        <v>956.7272223247217</v>
+        <v>1037.276562079218</v>
       </c>
       <c r="D7" t="n">
-        <v>1070.046366449722</v>
+        <v>1150.595706204218</v>
       </c>
       <c r="E7" t="n">
-        <v>1187.875270661135</v>
+        <v>1150.595706204218</v>
       </c>
       <c r="F7" t="n">
-        <v>1312.23624325307</v>
+        <v>1150.595706204218</v>
       </c>
       <c r="G7" t="n">
-        <v>1465.642809139955</v>
+        <v>1150.595706204218</v>
       </c>
       <c r="H7" t="n">
-        <v>1465.642809139955</v>
+        <v>1244.509930203872</v>
       </c>
       <c r="I7" t="n">
         <v>1465.642809139955</v>
@@ -4749,19 +4749,19 @@
         <v>290.525934252978</v>
       </c>
       <c r="U7" t="n">
-        <v>290.525934252978</v>
+        <v>537.0771268912647</v>
       </c>
       <c r="V7" t="n">
-        <v>489.347327138924</v>
+        <v>537.0771268912647</v>
       </c>
       <c r="W7" t="n">
-        <v>661.2382453986014</v>
+        <v>537.0771268912647</v>
       </c>
       <c r="X7" t="n">
-        <v>812.2690364227949</v>
+        <v>688.1079179154582</v>
       </c>
       <c r="Y7" t="n">
-        <v>812.2690364227949</v>
+        <v>799.5172185944905</v>
       </c>
     </row>
     <row r="8">
@@ -4771,16 +4771,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>245.2847218926082</v>
+        <v>1358.971397260877</v>
       </c>
       <c r="C8" t="n">
-        <v>96.87586368209487</v>
+        <v>904.9566717629029</v>
       </c>
       <c r="D8" t="n">
-        <v>86.43227202568094</v>
+        <v>894.513080106489</v>
       </c>
       <c r="E8" t="n">
-        <v>82.02490878641969</v>
+        <v>486.0653128268237</v>
       </c>
       <c r="F8" t="n">
         <v>77.08588988943801</v>
@@ -4795,22 +4795,22 @@
         <v>65.2</v>
       </c>
       <c r="J8" t="n">
-        <v>65.2</v>
+        <v>448.0719498394611</v>
       </c>
       <c r="K8" t="n">
-        <v>65.2</v>
+        <v>431.6896266071377</v>
       </c>
       <c r="L8" t="n">
-        <v>872.05</v>
+        <v>415.9503487525701</v>
       </c>
       <c r="M8" t="n">
-        <v>1376.888805967692</v>
+        <v>920.7891547202621</v>
       </c>
       <c r="N8" t="n">
-        <v>1360.50648273537</v>
+        <v>1530.078007668699</v>
       </c>
       <c r="O8" t="n">
-        <v>2167.35648273537</v>
+        <v>2336.928007668699</v>
       </c>
       <c r="P8" t="n">
         <v>2828.877889957487</v>
@@ -4822,25 +4822,25 @@
         <v>3260</v>
       </c>
       <c r="S8" t="n">
-        <v>3164.193769896644</v>
+        <v>3065.759233143699</v>
       </c>
       <c r="T8" t="n">
-        <v>2975.632576231427</v>
+        <v>2877.198039478483</v>
       </c>
       <c r="U8" t="n">
-        <v>2319.853488808588</v>
+        <v>2625.459356096048</v>
       </c>
       <c r="V8" t="n">
-        <v>1683.640333084524</v>
+        <v>2393.286604412388</v>
       </c>
       <c r="W8" t="n">
-        <v>1442.85904421488</v>
+        <v>2152.505315542744</v>
       </c>
       <c r="X8" t="n">
-        <v>1248.634970012185</v>
+        <v>1958.281241340049</v>
       </c>
       <c r="Y8" t="n">
-        <v>732.152714777027</v>
+        <v>1845.839390145295</v>
       </c>
     </row>
     <row r="9">
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>284.5195817084329</v>
+        <v>65.2</v>
       </c>
       <c r="C9" t="n">
-        <v>284.5195817084329</v>
+        <v>65.2</v>
       </c>
       <c r="D9" t="n">
-        <v>284.5195817084329</v>
+        <v>65.2</v>
       </c>
       <c r="E9" t="n">
-        <v>284.5195817084329</v>
+        <v>65.2</v>
       </c>
       <c r="F9" t="n">
-        <v>284.5195817084329</v>
+        <v>65.2</v>
       </c>
       <c r="G9" t="n">
-        <v>284.5195817084329</v>
+        <v>65.2</v>
       </c>
       <c r="H9" t="n">
-        <v>284.5195817084329</v>
+        <v>65.2</v>
       </c>
       <c r="I9" t="n">
         <v>65.2</v>
@@ -4898,28 +4898,28 @@
         <v>1220.632420368536</v>
       </c>
       <c r="R9" t="n">
-        <v>828.8414751317138</v>
+        <v>1013.562297463685</v>
       </c>
       <c r="S9" t="n">
-        <v>761.6051115310963</v>
+        <v>542.2855298226635</v>
       </c>
       <c r="T9" t="n">
-        <v>756.1932274730016</v>
+        <v>536.8736457645688</v>
       </c>
       <c r="U9" t="n">
-        <v>755.9807428667523</v>
+        <v>536.6611611583195</v>
       </c>
       <c r="V9" t="n">
-        <v>741.3235032793582</v>
+        <v>522.0039215709254</v>
       </c>
       <c r="W9" t="n">
-        <v>304.582954885592</v>
+        <v>85.26337317715914</v>
       </c>
       <c r="X9" t="n">
-        <v>284.5195817084329</v>
+        <v>65.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>284.5195817084329</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="10">
@@ -4929,25 +4929,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>722.9114816952028</v>
+        <v>924.0263740890871</v>
       </c>
       <c r="C10" t="n">
-        <v>848.9134875136386</v>
+        <v>1050.028379907523</v>
       </c>
       <c r="D10" t="n">
-        <v>848.9134875136386</v>
+        <v>1163.347524032523</v>
       </c>
       <c r="E10" t="n">
-        <v>966.7423917250517</v>
+        <v>1281.176428243936</v>
       </c>
       <c r="F10" t="n">
-        <v>1091.103364316987</v>
+        <v>1281.176428243936</v>
       </c>
       <c r="G10" t="n">
-        <v>1244.509930203872</v>
+        <v>1281.176428243936</v>
       </c>
       <c r="H10" t="n">
-        <v>1244.509930203872</v>
+        <v>1450.693013403333</v>
       </c>
       <c r="I10" t="n">
         <v>1465.642809139955</v>
@@ -4989,16 +4989,16 @@
         <v>290.525934252978</v>
       </c>
       <c r="V10" t="n">
-        <v>290.525934252978</v>
+        <v>489.347327138924</v>
       </c>
       <c r="W10" t="n">
-        <v>462.4168525126554</v>
+        <v>661.2382453986014</v>
       </c>
       <c r="X10" t="n">
-        <v>611.5021810161705</v>
+        <v>812.2690364227949</v>
       </c>
       <c r="Y10" t="n">
-        <v>722.9114816952028</v>
+        <v>812.2690364227949</v>
       </c>
     </row>
     <row r="11">
@@ -5008,22 +5008,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>953.3340975790759</v>
+        <v>849.6712852464634</v>
       </c>
       <c r="C11" t="n">
-        <v>799.0075518558202</v>
+        <v>622.9292870212171</v>
       </c>
       <c r="D11" t="n">
-        <v>611.7962834317295</v>
+        <v>622.9292870212171</v>
       </c>
       <c r="E11" t="n">
-        <v>430.6212434247915</v>
+        <v>441.754247014279</v>
       </c>
       <c r="F11" t="n">
-        <v>430.6212434247915</v>
+        <v>260.0475513496206</v>
       </c>
       <c r="G11" t="n">
-        <v>250.0582411146742</v>
+        <v>79.48454903950318</v>
       </c>
       <c r="H11" t="n">
         <v>65.2</v>
@@ -5032,22 +5032,22 @@
         <v>65.2</v>
       </c>
       <c r="J11" t="n">
-        <v>65.2</v>
+        <v>456.5091130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>83.63175644363446</v>
+        <v>1166.215479385524</v>
       </c>
       <c r="L11" t="n">
-        <v>83.63175644363446</v>
+        <v>1166.215479385524</v>
       </c>
       <c r="M11" t="n">
-        <v>594.4805851725695</v>
+        <v>1677.064308114459</v>
       </c>
       <c r="N11" t="n">
-        <v>1207.700904947333</v>
+        <v>2290.284627889223</v>
       </c>
       <c r="O11" t="n">
-        <v>2014.550904947333</v>
+        <v>2821.400904947332</v>
       </c>
       <c r="P11" t="n">
         <v>2821.400904947332</v>
@@ -5059,25 +5059,25 @@
         <v>3233.860001183541</v>
       </c>
       <c r="S11" t="n">
-        <v>3233.860001183541</v>
+        <v>2961.286094312508</v>
       </c>
       <c r="T11" t="n">
-        <v>2868.531130750648</v>
+        <v>2595.957223879615</v>
       </c>
       <c r="U11" t="n">
-        <v>2440.024770600536</v>
+        <v>2595.957223879615</v>
       </c>
       <c r="V11" t="n">
-        <v>2031.084342149199</v>
+        <v>2187.016795428278</v>
       </c>
       <c r="W11" t="n">
-        <v>1613.535376511878</v>
+        <v>1769.467829790957</v>
       </c>
       <c r="X11" t="n">
-        <v>1242.543625541507</v>
+        <v>1398.476078820586</v>
       </c>
       <c r="Y11" t="n">
-        <v>953.3340975790759</v>
+        <v>1109.266550858155</v>
       </c>
     </row>
     <row r="12">
@@ -5108,13 +5108,13 @@
         <v>65.2</v>
       </c>
       <c r="I12" t="n">
-        <v>65.2</v>
+        <v>72.99487796756496</v>
       </c>
       <c r="J12" t="n">
-        <v>411.906520175299</v>
+        <v>419.7013981428639</v>
       </c>
       <c r="K12" t="n">
-        <v>823.8493362696825</v>
+        <v>831.6442142372473</v>
       </c>
       <c r="L12" t="n">
         <v>1121.920378378698</v>
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>121.7463685221783</v>
+        <v>178.8982646830374</v>
       </c>
       <c r="C13" t="n">
-        <v>121.7463685221783</v>
+        <v>178.8982646830374</v>
       </c>
       <c r="D13" t="n">
-        <v>121.7463685221783</v>
+        <v>178.8982646830374</v>
       </c>
       <c r="E13" t="n">
+        <v>178.8982646830374</v>
+      </c>
+      <c r="F13" t="n">
+        <v>178.8982646830374</v>
+      </c>
+      <c r="G13" t="n">
+        <v>178.8982646830374</v>
+      </c>
+      <c r="H13" t="n">
+        <v>175.0890463985742</v>
+      </c>
+      <c r="I13" t="n">
+        <v>222.9719253346571</v>
+      </c>
+      <c r="J13" t="n">
+        <v>410.8056659871085</v>
+      </c>
+      <c r="K13" t="n">
+        <v>410.8056659871085</v>
+      </c>
+      <c r="L13" t="n">
+        <v>410.8056659871085</v>
+      </c>
+      <c r="M13" t="n">
+        <v>410.8056659871085</v>
+      </c>
+      <c r="N13" t="n">
+        <v>410.8056659871085</v>
+      </c>
+      <c r="O13" t="n">
+        <v>410.8056659871085</v>
+      </c>
+      <c r="P13" t="n">
+        <v>410.8056659871085</v>
+      </c>
+      <c r="Q13" t="n">
         <v>65.2</v>
       </c>
-      <c r="F13" t="n">
+      <c r="R13" t="n">
         <v>65.2</v>
       </c>
-      <c r="G13" t="n">
+      <c r="S13" t="n">
         <v>65.2</v>
       </c>
-      <c r="H13" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="I13" t="n">
-        <v>113.0828789360829</v>
-      </c>
-      <c r="J13" t="n">
-        <v>300.9166195885342</v>
-      </c>
-      <c r="K13" t="n">
-        <v>300.9166195885342</v>
-      </c>
-      <c r="L13" t="n">
-        <v>300.9166195885342</v>
-      </c>
-      <c r="M13" t="n">
-        <v>300.9166195885342</v>
-      </c>
-      <c r="N13" t="n">
-        <v>300.9166195885342</v>
-      </c>
-      <c r="O13" t="n">
-        <v>300.9166195885342</v>
-      </c>
-      <c r="P13" t="n">
-        <v>300.9166195885342</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>300.9166195885342</v>
-      </c>
-      <c r="R13" t="n">
-        <v>71.14441984869882</v>
-      </c>
-      <c r="S13" t="n">
-        <v>71.14441984869882</v>
-      </c>
       <c r="T13" t="n">
-        <v>85.97009900750368</v>
+        <v>80.02567915880486</v>
       </c>
       <c r="U13" t="n">
-        <v>159.2712916457903</v>
+        <v>153.3268717970915</v>
       </c>
       <c r="V13" t="n">
-        <v>184.8426845317363</v>
+        <v>178.8982646830374</v>
       </c>
       <c r="W13" t="n">
-        <v>184.8426845317363</v>
+        <v>178.8982646830374</v>
       </c>
       <c r="X13" t="n">
-        <v>184.8426845317363</v>
+        <v>178.8982646830374</v>
       </c>
       <c r="Y13" t="n">
-        <v>121.7463685221783</v>
+        <v>178.8982646830374</v>
       </c>
     </row>
     <row r="14">
@@ -5245,76 +5245,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>880.1835184729979</v>
+        <v>883.6685602764463</v>
       </c>
       <c r="C14" t="n">
-        <v>707.9869747932061</v>
+        <v>711.4720165966545</v>
       </c>
       <c r="D14" t="n">
-        <v>575.3211609145699</v>
+        <v>578.8062027180183</v>
       </c>
       <c r="E14" t="n">
-        <v>448.6915754530864</v>
+        <v>452.1766172565348</v>
       </c>
       <c r="F14" t="n">
-        <v>321.5303343338825</v>
+        <v>325.0153761373309</v>
       </c>
       <c r="G14" t="n">
-        <v>195.5127865692196</v>
+        <v>198.9978283726681</v>
       </c>
       <c r="H14" t="n">
-        <v>65.2</v>
+        <v>68.68504180344846</v>
       </c>
       <c r="I14" t="n">
         <v>65.2</v>
       </c>
       <c r="J14" t="n">
-        <v>65.2</v>
+        <v>456.5091130376557</v>
       </c>
       <c r="K14" t="n">
-        <v>774.9063663478685</v>
+        <v>1166.215479385524</v>
       </c>
       <c r="L14" t="n">
-        <v>1581.756366347868</v>
+        <v>1166.215479385524</v>
       </c>
       <c r="M14" t="n">
-        <v>2092.605195076803</v>
+        <v>1677.064308114459</v>
       </c>
       <c r="N14" t="n">
-        <v>2705.825514851566</v>
+        <v>2014.550904947333</v>
       </c>
       <c r="O14" t="n">
-        <v>2705.825514851566</v>
+        <v>2821.400904947332</v>
       </c>
       <c r="P14" t="n">
-        <v>3260</v>
+        <v>2821.400904947332</v>
       </c>
       <c r="Q14" t="n">
         <v>3260</v>
       </c>
       <c r="R14" t="n">
-        <v>3256.514958196551</v>
+        <v>3260</v>
       </c>
       <c r="S14" t="n">
-        <v>3038.486505870972</v>
+        <v>3041.971547674421</v>
       </c>
       <c r="T14" t="n">
-        <v>2727.703089983534</v>
+        <v>2731.188131786983</v>
       </c>
       <c r="U14" t="n">
-        <v>2353.742184378877</v>
+        <v>2357.227226182325</v>
       </c>
       <c r="V14" t="n">
-        <v>1999.347210472994</v>
+        <v>2002.832252276443</v>
       </c>
       <c r="W14" t="n">
-        <v>1636.343699381128</v>
+        <v>1639.828741184576</v>
       </c>
       <c r="X14" t="n">
-        <v>1319.897402956211</v>
+        <v>1323.382444759659</v>
       </c>
       <c r="Y14" t="n">
-        <v>1085.233329539235</v>
+        <v>1088.718371342683</v>
       </c>
     </row>
     <row r="15">
@@ -5345,28 +5345,28 @@
         <v>65.2</v>
       </c>
       <c r="I15" t="n">
-        <v>65.2</v>
+        <v>126.454877967565</v>
       </c>
       <c r="J15" t="n">
-        <v>465.3665201752989</v>
+        <v>250.4113981428639</v>
       </c>
       <c r="K15" t="n">
-        <v>654.5593362696823</v>
+        <v>439.6042142372473</v>
       </c>
       <c r="L15" t="n">
-        <v>1202.119797864882</v>
+        <v>710.9546758324475</v>
       </c>
       <c r="M15" t="n">
-        <v>1288.200339607742</v>
+        <v>797.0352175753068</v>
       </c>
       <c r="N15" t="n">
-        <v>1421.48062421531</v>
+        <v>1084.429386547307</v>
       </c>
       <c r="O15" t="n">
-        <v>1704.543365791451</v>
+        <v>1599.681838231026</v>
       </c>
       <c r="P15" t="n">
-        <v>1817.072710260958</v>
+        <v>1712.211182700533</v>
       </c>
       <c r="Q15" t="n">
         <v>1817.072710260958</v>
@@ -5403,55 +5403,55 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>405.873354586564</v>
+        <v>422.6199739669084</v>
       </c>
       <c r="C16" t="n">
-        <v>412.0853604049998</v>
+        <v>428.8319797853442</v>
       </c>
       <c r="D16" t="n">
-        <v>412.0853604049998</v>
+        <v>428.8319797853442</v>
       </c>
       <c r="E16" t="n">
-        <v>412.0853604049998</v>
+        <v>428.8319797853442</v>
       </c>
       <c r="F16" t="n">
-        <v>416.6563329969353</v>
+        <v>433.4029523772797</v>
       </c>
       <c r="G16" t="n">
-        <v>450.2728988838206</v>
+        <v>467.019518264165</v>
       </c>
       <c r="H16" t="n">
-        <v>499.9994840432182</v>
+        <v>516.7461034235625</v>
       </c>
       <c r="I16" t="n">
-        <v>601.342362979301</v>
+        <v>618.0889823596455</v>
       </c>
       <c r="J16" t="n">
-        <v>842.6361036317523</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="K16" t="n">
-        <v>833.0191603982745</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="L16" t="n">
-        <v>833.0191603982745</v>
+        <v>845.6113324106632</v>
       </c>
       <c r="M16" t="n">
-        <v>812.459801265491</v>
+        <v>601.5389976606127</v>
       </c>
       <c r="N16" t="n">
-        <v>517.3233615971224</v>
+        <v>601.5389976606127</v>
       </c>
       <c r="O16" t="n">
-        <v>517.3233615971224</v>
+        <v>601.5389976606127</v>
       </c>
       <c r="P16" t="n">
-        <v>517.3233615971224</v>
+        <v>601.5389976606127</v>
       </c>
       <c r="Q16" t="n">
-        <v>517.3233615971224</v>
+        <v>601.5389976606127</v>
       </c>
       <c r="R16" t="n">
-        <v>65.2</v>
+        <v>149.4156360634904</v>
       </c>
       <c r="S16" t="n">
         <v>65.2</v>
@@ -5472,7 +5472,7 @@
         <v>422.6199739669084</v>
       </c>
       <c r="Y16" t="n">
-        <v>414.0691125028051</v>
+        <v>422.6199739669084</v>
       </c>
     </row>
     <row r="17">
@@ -5497,34 +5497,34 @@
         <v>325.0153761373309</v>
       </c>
       <c r="G17" t="n">
-        <v>198.9978283726681</v>
+        <v>195.5127865692196</v>
       </c>
       <c r="H17" t="n">
-        <v>68.68504180344846</v>
+        <v>65.2</v>
       </c>
       <c r="I17" t="n">
         <v>65.2</v>
       </c>
       <c r="J17" t="n">
-        <v>65.2</v>
+        <v>456.5091130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>83.63175644363456</v>
+        <v>1166.215479385524</v>
       </c>
       <c r="L17" t="n">
-        <v>890.4817564436345</v>
+        <v>1973.065479385524</v>
       </c>
       <c r="M17" t="n">
-        <v>1401.330585172569</v>
+        <v>2483.914308114459</v>
       </c>
       <c r="N17" t="n">
-        <v>2014.550904947333</v>
+        <v>2483.914308114459</v>
       </c>
       <c r="O17" t="n">
-        <v>2821.400904947332</v>
+        <v>3260</v>
       </c>
       <c r="P17" t="n">
-        <v>2821.400904947332</v>
+        <v>3260</v>
       </c>
       <c r="Q17" t="n">
         <v>3260</v>
@@ -5582,28 +5582,28 @@
         <v>65.2</v>
       </c>
       <c r="I18" t="n">
-        <v>65.2</v>
+        <v>126.454877967565</v>
       </c>
       <c r="J18" t="n">
-        <v>189.156520175299</v>
+        <v>250.4113981428639</v>
       </c>
       <c r="K18" t="n">
-        <v>654.5593362696824</v>
+        <v>439.6042142372473</v>
       </c>
       <c r="L18" t="n">
-        <v>925.9097978648824</v>
+        <v>710.9546758324475</v>
       </c>
       <c r="M18" t="n">
-        <v>1011.990339607742</v>
+        <v>797.0352175753068</v>
       </c>
       <c r="N18" t="n">
-        <v>1145.27062421531</v>
+        <v>1084.429386547307</v>
       </c>
       <c r="O18" t="n">
-        <v>1660.523075899029</v>
+        <v>1323.471838231026</v>
       </c>
       <c r="P18" t="n">
-        <v>1773.052420368535</v>
+        <v>1712.211182700533</v>
       </c>
       <c r="Q18" t="n">
         <v>1817.072710260958</v>
@@ -5640,52 +5640,52 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>414.0691125028051</v>
+        <v>422.6199739669084</v>
       </c>
       <c r="C19" t="n">
-        <v>420.2811183212409</v>
+        <v>428.8319797853442</v>
       </c>
       <c r="D19" t="n">
-        <v>413.6788778610838</v>
+        <v>428.8319797853442</v>
       </c>
       <c r="E19" t="n">
-        <v>413.6788778610838</v>
+        <v>428.8319797853442</v>
       </c>
       <c r="F19" t="n">
-        <v>418.2498504530193</v>
+        <v>433.4029523772797</v>
       </c>
       <c r="G19" t="n">
-        <v>451.8664163399046</v>
+        <v>467.019518264165</v>
       </c>
       <c r="H19" t="n">
-        <v>501.5930014993021</v>
+        <v>516.7461034235625</v>
       </c>
       <c r="I19" t="n">
-        <v>602.9358804353851</v>
+        <v>618.0889823596455</v>
       </c>
       <c r="J19" t="n">
-        <v>844.2296210878364</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="K19" t="n">
-        <v>844.2296210878364</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="L19" t="n">
-        <v>844.2296210878364</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="M19" t="n">
-        <v>844.2296210878364</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="N19" t="n">
-        <v>844.2296210878364</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="O19" t="n">
-        <v>479.1330917150941</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="P19" t="n">
-        <v>149.4156360634904</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="Q19" t="n">
-        <v>149.4156360634904</v>
+        <v>601.5389976606127</v>
       </c>
       <c r="R19" t="n">
         <v>149.4156360634904</v>
@@ -5709,7 +5709,7 @@
         <v>422.6199739669084</v>
       </c>
       <c r="Y19" t="n">
-        <v>414.0691125028051</v>
+        <v>422.6199739669084</v>
       </c>
     </row>
     <row r="20">
@@ -5743,25 +5743,25 @@
         <v>65.2</v>
       </c>
       <c r="J20" t="n">
-        <v>65.2</v>
+        <v>456.5091130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>522.2308514963021</v>
+        <v>1166.215479385524</v>
       </c>
       <c r="L20" t="n">
-        <v>522.2308514963021</v>
+        <v>1697.331756443634</v>
       </c>
       <c r="M20" t="n">
-        <v>1033.079680225237</v>
+        <v>2208.180585172569</v>
       </c>
       <c r="N20" t="n">
-        <v>1646.3</v>
+        <v>2821.400904947332</v>
       </c>
       <c r="O20" t="n">
-        <v>2453.15</v>
+        <v>2821.400904947332</v>
       </c>
       <c r="P20" t="n">
-        <v>3260</v>
+        <v>2821.400904947332</v>
       </c>
       <c r="Q20" t="n">
         <v>3260</v>
@@ -5819,28 +5819,28 @@
         <v>65.2</v>
       </c>
       <c r="I21" t="n">
-        <v>65.2</v>
+        <v>126.454877967565</v>
       </c>
       <c r="J21" t="n">
-        <v>189.156520175299</v>
+        <v>250.4113981428639</v>
       </c>
       <c r="K21" t="n">
-        <v>654.5593362696824</v>
+        <v>593.7180986016792</v>
       </c>
       <c r="L21" t="n">
-        <v>969.9300877573045</v>
+        <v>1141.278560196879</v>
       </c>
       <c r="M21" t="n">
-        <v>1056.010629500164</v>
+        <v>1227.359101939739</v>
       </c>
       <c r="N21" t="n">
-        <v>1189.290914107732</v>
+        <v>1360.639386547307</v>
       </c>
       <c r="O21" t="n">
-        <v>1428.333365791451</v>
+        <v>1599.681838231026</v>
       </c>
       <c r="P21" t="n">
-        <v>1817.072710260958</v>
+        <v>1712.211182700533</v>
       </c>
       <c r="Q21" t="n">
         <v>1817.072710260958</v>
@@ -5877,49 +5877,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>414.0691125028051</v>
+        <v>405.873354586564</v>
       </c>
       <c r="C22" t="n">
-        <v>420.2811183212409</v>
+        <v>412.0853604049998</v>
       </c>
       <c r="D22" t="n">
-        <v>420.2811183212409</v>
+        <v>405.4831199448427</v>
       </c>
       <c r="E22" t="n">
-        <v>420.2811183212409</v>
+        <v>403.4822059681189</v>
       </c>
       <c r="F22" t="n">
-        <v>424.8520909131764</v>
+        <v>408.0531785600544</v>
       </c>
       <c r="G22" t="n">
-        <v>458.4686568000616</v>
+        <v>441.6697444469397</v>
       </c>
       <c r="H22" t="n">
-        <v>508.1952419594592</v>
+        <v>491.3963296063373</v>
       </c>
       <c r="I22" t="n">
-        <v>609.5381208955421</v>
+        <v>592.7392085424202</v>
       </c>
       <c r="J22" t="n">
-        <v>850.8318615479934</v>
+        <v>834.0329491948715</v>
       </c>
       <c r="K22" t="n">
-        <v>850.8318615479934</v>
+        <v>824.4160059613937</v>
       </c>
       <c r="L22" t="n">
-        <v>850.8318615479934</v>
+        <v>678.4083007515158</v>
       </c>
       <c r="M22" t="n">
-        <v>850.8318615479934</v>
+        <v>434.3359660014654</v>
       </c>
       <c r="N22" t="n">
-        <v>850.8318615479934</v>
+        <v>139.1995263330967</v>
       </c>
       <c r="O22" t="n">
-        <v>850.8318615479934</v>
+        <v>65.2</v>
       </c>
       <c r="P22" t="n">
-        <v>438.2582278830666</v>
+        <v>65.2</v>
       </c>
       <c r="Q22" t="n">
         <v>65.2</v>
@@ -5956,46 +5956,46 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>883.6685602764463</v>
+        <v>880.1835184729979</v>
       </c>
       <c r="C23" t="n">
-        <v>711.4720165966545</v>
+        <v>707.9869747932061</v>
       </c>
       <c r="D23" t="n">
-        <v>578.8062027180183</v>
+        <v>575.3211609145699</v>
       </c>
       <c r="E23" t="n">
-        <v>452.1766172565348</v>
+        <v>448.6915754530864</v>
       </c>
       <c r="F23" t="n">
-        <v>325.0153761373309</v>
+        <v>321.5303343338825</v>
       </c>
       <c r="G23" t="n">
-        <v>198.9978283726681</v>
+        <v>195.5127865692196</v>
       </c>
       <c r="H23" t="n">
-        <v>68.68504180344846</v>
+        <v>65.2</v>
       </c>
       <c r="I23" t="n">
         <v>65.2</v>
       </c>
       <c r="J23" t="n">
-        <v>65.2</v>
+        <v>456.5091130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>774.9063663478685</v>
+        <v>1166.215479385524</v>
       </c>
       <c r="L23" t="n">
-        <v>1401.330585172569</v>
+        <v>1973.065479385524</v>
       </c>
       <c r="M23" t="n">
-        <v>1401.330585172569</v>
+        <v>1973.065479385524</v>
       </c>
       <c r="N23" t="n">
         <v>2014.550904947333</v>
       </c>
       <c r="O23" t="n">
-        <v>2014.550904947333</v>
+        <v>2821.400904947332</v>
       </c>
       <c r="P23" t="n">
         <v>2821.400904947332</v>
@@ -6004,28 +6004,28 @@
         <v>3260</v>
       </c>
       <c r="R23" t="n">
-        <v>3260</v>
+        <v>3256.514958196551</v>
       </c>
       <c r="S23" t="n">
-        <v>3041.971547674421</v>
+        <v>3038.486505870972</v>
       </c>
       <c r="T23" t="n">
-        <v>2731.188131786983</v>
+        <v>2727.703089983534</v>
       </c>
       <c r="U23" t="n">
-        <v>2357.227226182325</v>
+        <v>2353.742184378877</v>
       </c>
       <c r="V23" t="n">
-        <v>2002.832252276443</v>
+        <v>1999.347210472994</v>
       </c>
       <c r="W23" t="n">
-        <v>1639.828741184576</v>
+        <v>1636.343699381128</v>
       </c>
       <c r="X23" t="n">
-        <v>1323.382444759659</v>
+        <v>1319.897402956211</v>
       </c>
       <c r="Y23" t="n">
-        <v>1088.718371342683</v>
+        <v>1085.233329539235</v>
       </c>
     </row>
     <row r="24">
@@ -6056,28 +6056,28 @@
         <v>65.2</v>
       </c>
       <c r="I24" t="n">
-        <v>65.2</v>
+        <v>126.454877967565</v>
       </c>
       <c r="J24" t="n">
-        <v>233.1768100677209</v>
+        <v>526.6213981428639</v>
       </c>
       <c r="K24" t="n">
-        <v>422.3696261621043</v>
+        <v>715.8142142372473</v>
       </c>
       <c r="L24" t="n">
-        <v>693.7200877573044</v>
+        <v>1141.278560196879</v>
       </c>
       <c r="M24" t="n">
-        <v>779.8006295001637</v>
+        <v>1227.359101939739</v>
       </c>
       <c r="N24" t="n">
-        <v>1189.290914107732</v>
+        <v>1360.639386547307</v>
       </c>
       <c r="O24" t="n">
-        <v>1428.333365791451</v>
+        <v>1599.681838231026</v>
       </c>
       <c r="P24" t="n">
-        <v>1817.072710260958</v>
+        <v>1712.211182700533</v>
       </c>
       <c r="Q24" t="n">
         <v>1817.072710260958</v>
@@ -6141,25 +6141,25 @@
         <v>850.779568575216</v>
       </c>
       <c r="K25" t="n">
-        <v>850.779568575216</v>
+        <v>841.1626253417381</v>
       </c>
       <c r="L25" t="n">
-        <v>850.779568575216</v>
+        <v>695.1549201318602</v>
       </c>
       <c r="M25" t="n">
-        <v>812.459801265491</v>
+        <v>451.0825853818098</v>
       </c>
       <c r="N25" t="n">
-        <v>517.3233615971224</v>
+        <v>451.0825853818098</v>
       </c>
       <c r="O25" t="n">
-        <v>517.3233615971224</v>
+        <v>451.0825853818098</v>
       </c>
       <c r="P25" t="n">
-        <v>517.3233615971224</v>
+        <v>451.0825853818098</v>
       </c>
       <c r="Q25" t="n">
-        <v>517.3233615971224</v>
+        <v>451.0825853818098</v>
       </c>
       <c r="R25" t="n">
         <v>65.2</v>
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>902.0890611409357</v>
+        <v>790.622979096388</v>
       </c>
       <c r="C26" t="n">
-        <v>675.3470629156893</v>
+        <v>790.622979096388</v>
       </c>
       <c r="D26" t="n">
-        <v>488.1357944915986</v>
+        <v>790.622979096388</v>
       </c>
       <c r="E26" t="n">
-        <v>306.9607544846606</v>
+        <v>609.44793908945</v>
       </c>
       <c r="F26" t="n">
-        <v>125.2540588200021</v>
+        <v>427.7412434247915</v>
       </c>
       <c r="G26" t="n">
-        <v>125.2540588200021</v>
+        <v>247.1782411146742</v>
       </c>
       <c r="H26" t="n">
         <v>62.32</v>
@@ -6217,25 +6217,25 @@
         <v>62.32</v>
       </c>
       <c r="J26" t="n">
-        <v>453.6291130376557</v>
+        <v>250.6533138773436</v>
       </c>
       <c r="K26" t="n">
-        <v>453.6291130376557</v>
+        <v>960.3596802252121</v>
       </c>
       <c r="L26" t="n">
-        <v>624.1320762183474</v>
+        <v>1731.569680225212</v>
       </c>
       <c r="M26" t="n">
-        <v>1134.980904947282</v>
+        <v>1731.569680225212</v>
       </c>
       <c r="N26" t="n">
-        <v>1134.980904947282</v>
+        <v>2344.789999999975</v>
       </c>
       <c r="O26" t="n">
-        <v>1906.190904947307</v>
+        <v>3116</v>
       </c>
       <c r="P26" t="n">
-        <v>2677.400904947332</v>
+        <v>3116</v>
       </c>
       <c r="Q26" t="n">
         <v>3116</v>
@@ -6247,22 +6247,22 @@
         <v>2817.286094312508</v>
       </c>
       <c r="T26" t="n">
-        <v>2817.286094312508</v>
+        <v>2676.205749917221</v>
       </c>
       <c r="U26" t="n">
-        <v>2388.779734162396</v>
+        <v>2247.699389767109</v>
       </c>
       <c r="V26" t="n">
-        <v>1979.839305711059</v>
+        <v>1838.758961315772</v>
       </c>
       <c r="W26" t="n">
-        <v>1562.290340073738</v>
+        <v>1421.209995678451</v>
       </c>
       <c r="X26" t="n">
-        <v>1191.298589103366</v>
+        <v>1050.21824470808</v>
       </c>
       <c r="Y26" t="n">
-        <v>902.0890611409357</v>
+        <v>1050.21824470808</v>
       </c>
     </row>
     <row r="27">
@@ -6293,22 +6293,22 @@
         <v>62.32</v>
       </c>
       <c r="I27" t="n">
-        <v>62.32</v>
+        <v>70.11487796756495</v>
       </c>
       <c r="J27" t="n">
-        <v>212.9971006891147</v>
+        <v>416.8213981428639</v>
       </c>
       <c r="K27" t="n">
-        <v>624.9399167834981</v>
+        <v>828.7642142372474</v>
       </c>
       <c r="L27" t="n">
-        <v>1119.040378378698</v>
+        <v>1322.864675832448</v>
       </c>
       <c r="M27" t="n">
-        <v>1427.870920121557</v>
+        <v>1631.695217575307</v>
       </c>
       <c r="N27" t="n">
-        <v>1783.901204729126</v>
+        <v>1987.725502182875</v>
       </c>
       <c r="O27" t="n">
         <v>2245.693656412845</v>
@@ -6369,25 +6369,25 @@
         <v>155.7719284794717</v>
       </c>
       <c r="H28" t="n">
-        <v>155.7719284794717</v>
+        <v>151.9627101950085</v>
       </c>
       <c r="I28" t="n">
-        <v>203.6548074155546</v>
+        <v>199.8455891310914</v>
       </c>
       <c r="J28" t="n">
-        <v>391.488548068006</v>
+        <v>387.6793297835427</v>
       </c>
       <c r="K28" t="n">
-        <v>391.488548068006</v>
+        <v>323.5169320046103</v>
       </c>
       <c r="L28" t="n">
-        <v>391.488548068006</v>
+        <v>122.9637722492778</v>
       </c>
       <c r="M28" t="n">
-        <v>391.488548068006</v>
+        <v>62.32</v>
       </c>
       <c r="N28" t="n">
-        <v>391.488548068006</v>
+        <v>62.32</v>
       </c>
       <c r="O28" t="n">
         <v>62.32</v>
@@ -6430,13 +6430,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>846.5211162073476</v>
+        <v>892.0880744256559</v>
       </c>
       <c r="C29" t="n">
-        <v>846.5211162073476</v>
+        <v>691.6087024630358</v>
       </c>
       <c r="D29" t="n">
-        <v>685.5724740458832</v>
+        <v>530.6600603015713</v>
       </c>
       <c r="E29" t="n">
         <v>530.6600603015713</v>
@@ -6457,19 +6457,19 @@
         <v>453.6291130376557</v>
       </c>
       <c r="K29" t="n">
-        <v>453.6291130376557</v>
+        <v>1163.335479385524</v>
       </c>
       <c r="L29" t="n">
-        <v>453.6291130376557</v>
+        <v>1163.335479385524</v>
       </c>
       <c r="M29" t="n">
-        <v>964.4779417665907</v>
+        <v>1674.184308114459</v>
       </c>
       <c r="N29" t="n">
-        <v>1134.980904947269</v>
+        <v>1906.190904947301</v>
       </c>
       <c r="O29" t="n">
-        <v>1906.190904947301</v>
+        <v>2677.400904947332</v>
       </c>
       <c r="P29" t="n">
         <v>2677.400904947332</v>
@@ -6481,25 +6481,25 @@
         <v>3116</v>
       </c>
       <c r="S29" t="n">
-        <v>3116</v>
+        <v>2985.423958103624</v>
       </c>
       <c r="T29" t="n">
-        <v>2776.933755829733</v>
+        <v>2646.357713933357</v>
       </c>
       <c r="U29" t="n">
-        <v>2374.690021942248</v>
+        <v>2244.113980045872</v>
       </c>
       <c r="V29" t="n">
-        <v>2078.816121338657</v>
+        <v>1861.436177857161</v>
       </c>
       <c r="W29" t="n">
-        <v>1687.529781963962</v>
+        <v>1470.149838482466</v>
       </c>
       <c r="X29" t="n">
-        <v>1342.800657256217</v>
+        <v>1125.420713774721</v>
       </c>
       <c r="Y29" t="n">
-        <v>1079.853755556413</v>
+        <v>1125.420713774721</v>
       </c>
     </row>
     <row r="30">
@@ -6533,25 +6533,25 @@
         <v>95.85487796756496</v>
       </c>
       <c r="J30" t="n">
-        <v>461.4892343101459</v>
+        <v>468.3013981428639</v>
       </c>
       <c r="K30" t="n">
-        <v>899.1720504045293</v>
+        <v>657.4942142372473</v>
       </c>
       <c r="L30" t="n">
-        <v>1170.522511999729</v>
+        <v>1177.334675832447</v>
       </c>
       <c r="M30" t="n">
-        <v>1505.093053742589</v>
+        <v>1511.905217575307</v>
       </c>
       <c r="N30" t="n">
-        <v>1886.863338350157</v>
+        <v>1645.185502182875</v>
       </c>
       <c r="O30" t="n">
-        <v>2125.905790033876</v>
+        <v>1884.227953866594</v>
       </c>
       <c r="P30" t="n">
-        <v>2238.435134503382</v>
+        <v>2161.293606942957</v>
       </c>
       <c r="Q30" t="n">
         <v>2238.435134503382</v>
@@ -6618,13 +6618,13 @@
         <v>596.2397446017254</v>
       </c>
       <c r="L31" t="n">
-        <v>503.1764619477551</v>
+        <v>596.2397446017254</v>
       </c>
       <c r="M31" t="n">
-        <v>503.1764619477551</v>
+        <v>596.2397446017254</v>
       </c>
       <c r="N31" t="n">
-        <v>503.1764619477551</v>
+        <v>596.2397446017254</v>
       </c>
       <c r="O31" t="n">
         <v>503.1764619477551</v>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>822.7580639275434</v>
+        <v>812.3958330037195</v>
       </c>
       <c r="C32" t="n">
         <v>659.6524293386606</v>
@@ -6694,16 +6694,16 @@
         <v>453.6291130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>453.6291130376557</v>
+        <v>1162.373874771057</v>
       </c>
       <c r="L32" t="n">
-        <v>521.7605851724787</v>
+        <v>1162.373874771057</v>
       </c>
       <c r="M32" t="n">
-        <v>521.7605851724787</v>
+        <v>1292.970585172524</v>
       </c>
       <c r="N32" t="n">
-        <v>1134.980904947242</v>
+        <v>1906.190904947287</v>
       </c>
       <c r="O32" t="n">
         <v>1906.190904947287</v>
@@ -6724,19 +6724,19 @@
         <v>2605.369949968801</v>
       </c>
       <c r="U32" t="n">
-        <v>2250.862184378877</v>
+        <v>2240.499953455053</v>
       </c>
       <c r="V32" t="n">
-        <v>1905.558119563903</v>
+        <v>1895.195888640079</v>
       </c>
       <c r="W32" t="n">
-        <v>1551.645517562946</v>
+        <v>1541.283286639122</v>
       </c>
       <c r="X32" t="n">
-        <v>1244.290130228938</v>
+        <v>1233.927899305114</v>
       </c>
       <c r="Y32" t="n">
-        <v>1018.716965902871</v>
+        <v>1008.354734979047</v>
       </c>
     </row>
     <row r="33">
@@ -6767,25 +6767,25 @@
         <v>62.32</v>
       </c>
       <c r="I33" t="n">
-        <v>62.32</v>
+        <v>123.5051259683603</v>
       </c>
       <c r="J33" t="n">
-        <v>186.2765201752989</v>
+        <v>247.4616461436593</v>
       </c>
       <c r="K33" t="n">
-        <v>375.4693362696823</v>
+        <v>436.6544622380427</v>
       </c>
       <c r="L33" t="n">
-        <v>646.8197978648825</v>
+        <v>993.1249238332429</v>
       </c>
       <c r="M33" t="n">
-        <v>732.9003396077418</v>
+        <v>1079.205465576102</v>
       </c>
       <c r="N33" t="n">
-        <v>866.1806242153101</v>
+        <v>1212.48575018367</v>
       </c>
       <c r="O33" t="n">
-        <v>1390.343075899029</v>
+        <v>1451.528201867389</v>
       </c>
       <c r="P33" t="n">
         <v>1564.057546336896</v>
@@ -6852,28 +6852,28 @@
         <v>965.3074096938342</v>
       </c>
       <c r="K34" t="n">
-        <v>965.3074096938342</v>
+        <v>964.7813755512655</v>
       </c>
       <c r="L34" t="n">
-        <v>965.3074096938342</v>
+        <v>827.8645794322965</v>
       </c>
       <c r="M34" t="n">
-        <v>965.3074096938342</v>
+        <v>592.8831537731552</v>
       </c>
       <c r="N34" t="n">
-        <v>965.3074096938342</v>
+        <v>505.3524525062132</v>
       </c>
       <c r="O34" t="n">
-        <v>965.3074096938342</v>
+        <v>505.3524525062132</v>
       </c>
       <c r="P34" t="n">
-        <v>561.8246851198165</v>
+        <v>505.3524525062132</v>
       </c>
       <c r="Q34" t="n">
-        <v>561.8246851198165</v>
+        <v>505.3524525062132</v>
       </c>
       <c r="R34" t="n">
-        <v>137.4447269725813</v>
+        <v>62.32</v>
       </c>
       <c r="S34" t="n">
         <v>62.32</v>
@@ -6904,10 +6904,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>812.3958330037195</v>
+        <v>822.7580639275434</v>
       </c>
       <c r="C35" t="n">
-        <v>649.2901984148368</v>
+        <v>659.6524293386606</v>
       </c>
       <c r="D35" t="n">
         <v>536.0775245509335</v>
@@ -6934,19 +6934,19 @@
         <v>1163.335479385524</v>
       </c>
       <c r="L35" t="n">
-        <v>1731.569680225167</v>
+        <v>1553.331756443634</v>
       </c>
       <c r="M35" t="n">
-        <v>1731.569680225167</v>
+        <v>2064.180585172569</v>
       </c>
       <c r="N35" t="n">
-        <v>2344.78999999993</v>
+        <v>2677.400904947332</v>
       </c>
       <c r="O35" t="n">
-        <v>3116</v>
+        <v>2677.400904947332</v>
       </c>
       <c r="P35" t="n">
-        <v>3116</v>
+        <v>2677.400904947332</v>
       </c>
       <c r="Q35" t="n">
         <v>3116</v>
@@ -6958,22 +6958,22 @@
         <v>2907.06245676533</v>
       </c>
       <c r="T35" t="n">
-        <v>2605.369949968801</v>
+        <v>2615.732180892625</v>
       </c>
       <c r="U35" t="n">
-        <v>2240.499953455053</v>
+        <v>2250.862184378877</v>
       </c>
       <c r="V35" t="n">
-        <v>1895.195888640079</v>
+        <v>1905.558119563903</v>
       </c>
       <c r="W35" t="n">
-        <v>1541.283286639122</v>
+        <v>1551.645517562946</v>
       </c>
       <c r="X35" t="n">
-        <v>1233.927899305114</v>
+        <v>1244.290130228938</v>
       </c>
       <c r="Y35" t="n">
-        <v>1008.354734979047</v>
+        <v>1018.716965902871</v>
       </c>
     </row>
     <row r="36">
@@ -7004,16 +7004,16 @@
         <v>62.32</v>
       </c>
       <c r="I36" t="n">
-        <v>123.5051259683605</v>
+        <v>132.484877967565</v>
       </c>
       <c r="J36" t="n">
-        <v>532.5816461436594</v>
+        <v>256.4413981428639</v>
       </c>
       <c r="K36" t="n">
-        <v>721.7744622380428</v>
+        <v>445.6342142372473</v>
       </c>
       <c r="L36" t="n">
-        <v>993.1249238332429</v>
+        <v>716.9846758324475</v>
       </c>
       <c r="M36" t="n">
         <v>1079.205465576102</v>
@@ -7095,22 +7095,22 @@
         <v>965.3074096938342</v>
       </c>
       <c r="M37" t="n">
-        <v>730.3259840346929</v>
+        <v>965.3074096938342</v>
       </c>
       <c r="N37" t="n">
-        <v>730.3259840346929</v>
+        <v>679.2618791163746</v>
       </c>
       <c r="O37" t="n">
-        <v>580.4771794787945</v>
+        <v>465.8027245740176</v>
       </c>
       <c r="P37" t="n">
-        <v>580.4771794787945</v>
+        <v>62.32</v>
       </c>
       <c r="Q37" t="n">
-        <v>580.4771794787945</v>
+        <v>62.32</v>
       </c>
       <c r="R37" t="n">
-        <v>137.4447269725813</v>
+        <v>62.32</v>
       </c>
       <c r="S37" t="n">
         <v>62.32</v>
@@ -7141,19 +7141,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>822.7580639275345</v>
+        <v>822.7580639275434</v>
       </c>
       <c r="C38" t="n">
-        <v>659.6524293386517</v>
+        <v>659.6524293386606</v>
       </c>
       <c r="D38" t="n">
-        <v>536.0775245509246</v>
+        <v>536.0775245509335</v>
       </c>
       <c r="E38" t="n">
-        <v>418.5388481803502</v>
+        <v>418.5388481803591</v>
       </c>
       <c r="F38" t="n">
-        <v>300.4685161520554</v>
+        <v>300.4685161520642</v>
       </c>
       <c r="G38" t="n">
         <v>183.5418774783105</v>
@@ -7168,19 +7168,19 @@
         <v>453.6291130376557</v>
       </c>
       <c r="K38" t="n">
-        <v>452.6675084231834</v>
+        <v>1163.335479385524</v>
       </c>
       <c r="L38" t="n">
-        <v>1223.877508423183</v>
+        <v>1163.335479385524</v>
       </c>
       <c r="M38" t="n">
-        <v>1734.726337152118</v>
+        <v>1674.184308114459</v>
       </c>
       <c r="N38" t="n">
-        <v>1734.726337152118</v>
+        <v>2287.404627889222</v>
       </c>
       <c r="O38" t="n">
-        <v>1906.190904947243</v>
+        <v>2239.08278795398</v>
       </c>
       <c r="P38" t="n">
         <v>2677.400904947332</v>
@@ -7189,28 +7189,28 @@
         <v>3116</v>
       </c>
       <c r="R38" t="n">
-        <v>3116</v>
+        <v>3116.000000000368</v>
       </c>
       <c r="S38" t="n">
-        <v>2907.06245676533</v>
+        <v>2917.424687689154</v>
       </c>
       <c r="T38" t="n">
-        <v>2605.369949968801</v>
+        <v>2615.732180892625</v>
       </c>
       <c r="U38" t="n">
-        <v>2240.499953455053</v>
+        <v>2250.862184378877</v>
       </c>
       <c r="V38" t="n">
-        <v>1895.195888640079</v>
+        <v>1905.558119563903</v>
       </c>
       <c r="W38" t="n">
-        <v>1541.283286639122</v>
+        <v>1551.645517562946</v>
       </c>
       <c r="X38" t="n">
-        <v>1233.927899305114</v>
+        <v>1244.290130228938</v>
       </c>
       <c r="Y38" t="n">
-        <v>1018.716965902862</v>
+        <v>1018.716965902871</v>
       </c>
     </row>
     <row r="39">
@@ -7241,28 +7241,28 @@
         <v>62.32</v>
       </c>
       <c r="I39" t="n">
-        <v>62.32</v>
+        <v>132.484877967565</v>
       </c>
       <c r="J39" t="n">
-        <v>186.2765201752989</v>
+        <v>256.4413981428639</v>
       </c>
       <c r="K39" t="n">
-        <v>375.4693362696823</v>
+        <v>445.6342142372473</v>
       </c>
       <c r="L39" t="n">
-        <v>821.7764513936685</v>
+        <v>716.9846758324475</v>
       </c>
       <c r="M39" t="n">
-        <v>907.8569931365278</v>
+        <v>803.0652175753067</v>
       </c>
       <c r="N39" t="n">
-        <v>1326.257277744096</v>
+        <v>936.3455021828751</v>
       </c>
       <c r="O39" t="n">
-        <v>1565.299729427815</v>
+        <v>1175.387953866594</v>
       </c>
       <c r="P39" t="n">
-        <v>1677.829073897321</v>
+        <v>1564.057546336896</v>
       </c>
       <c r="Q39" t="n">
         <v>1677.829073897321</v>
@@ -7326,25 +7326,25 @@
         <v>965.3074096938342</v>
       </c>
       <c r="K40" t="n">
-        <v>964.7813755512655</v>
+        <v>965.3074096938342</v>
       </c>
       <c r="L40" t="n">
-        <v>964.7813755512655</v>
+        <v>965.3074096938342</v>
       </c>
       <c r="M40" t="n">
-        <v>964.7813755512655</v>
+        <v>965.3074096938342</v>
       </c>
       <c r="N40" t="n">
-        <v>964.7813755512655</v>
+        <v>965.3074096938342</v>
       </c>
       <c r="O40" t="n">
-        <v>964.7813755512655</v>
+        <v>965.3074096938342</v>
       </c>
       <c r="P40" t="n">
-        <v>579.7066122509631</v>
+        <v>965.3074096938342</v>
       </c>
       <c r="Q40" t="n">
-        <v>137.4447269725813</v>
+        <v>580.4771794787945</v>
       </c>
       <c r="R40" t="n">
         <v>137.4447269725813</v>
@@ -7378,19 +7378,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>490.7003313402687</v>
+        <v>62.32</v>
       </c>
       <c r="C41" t="n">
-        <v>490.7003313402687</v>
+        <v>62.32</v>
       </c>
       <c r="D41" t="n">
-        <v>273.1860326131477</v>
+        <v>62.32</v>
       </c>
       <c r="E41" t="n">
-        <v>273.1860326131477</v>
+        <v>62.32</v>
       </c>
       <c r="F41" t="n">
-        <v>273.1860326131477</v>
+        <v>62.32</v>
       </c>
       <c r="G41" t="n">
         <v>62.32</v>
@@ -7405,16 +7405,16 @@
         <v>453.6291130376557</v>
       </c>
       <c r="K41" t="n">
-        <v>453.6291130376557</v>
+        <v>1163.335479385524</v>
       </c>
       <c r="L41" t="n">
-        <v>1224.839113037656</v>
+        <v>1906.190904947197</v>
       </c>
       <c r="M41" t="n">
-        <v>1224.839113037656</v>
+        <v>1906.190904947197</v>
       </c>
       <c r="N41" t="n">
-        <v>1224.839113037656</v>
+        <v>1906.190904947197</v>
       </c>
       <c r="O41" t="n">
         <v>1906.190904947197</v>
@@ -7429,25 +7429,25 @@
         <v>3116</v>
       </c>
       <c r="S41" t="n">
-        <v>2813.123062825936</v>
+        <v>2814.562381337368</v>
       </c>
       <c r="T41" t="n">
-        <v>2417.491162090013</v>
+        <v>2418.930480601445</v>
       </c>
       <c r="U41" t="n">
-        <v>1958.681771636871</v>
+        <v>1960.121090148303</v>
       </c>
       <c r="V41" t="n">
-        <v>1519.438312882504</v>
+        <v>1520.877631393936</v>
       </c>
       <c r="W41" t="n">
-        <v>1181.893408528392</v>
+        <v>1073.025635453585</v>
       </c>
       <c r="X41" t="n">
-        <v>780.5986272549904</v>
+        <v>671.7308541801827</v>
       </c>
       <c r="Y41" t="n">
-        <v>780.5986272549904</v>
+        <v>352.2182959147218</v>
       </c>
     </row>
     <row r="42">
@@ -7457,16 +7457,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>677.5438467636556</v>
+        <v>972.804795813948</v>
       </c>
       <c r="C42" t="n">
-        <v>509.7661574247472</v>
+        <v>805.0271064750395</v>
       </c>
       <c r="D42" t="n">
-        <v>355.2836454068657</v>
+        <v>650.5445944571582</v>
       </c>
       <c r="E42" t="n">
-        <v>355.2836454068657</v>
+        <v>501.3808598895696</v>
       </c>
       <c r="F42" t="n">
         <v>355.2836454068657</v>
@@ -7487,46 +7487,46 @@
         <v>761.5693362696824</v>
       </c>
       <c r="L42" t="n">
-        <v>1211.109050043319</v>
+        <v>1225.969797864882</v>
       </c>
       <c r="M42" t="n">
-        <v>1490.239591786179</v>
+        <v>1505.100339607742</v>
       </c>
       <c r="N42" t="n">
-        <v>1623.519876393747</v>
+        <v>1831.43062421531</v>
       </c>
       <c r="O42" t="n">
-        <v>2055.612328077466</v>
+        <v>2263.523075899029</v>
       </c>
       <c r="P42" t="n">
-        <v>2361.191672546973</v>
+        <v>2455.389860814817</v>
       </c>
       <c r="Q42" t="n">
-        <v>2382.893200107398</v>
+        <v>2477.091388375242</v>
       </c>
       <c r="R42" t="n">
-        <v>2027.061081630247</v>
+        <v>2239.359827154422</v>
       </c>
       <c r="S42" t="n">
-        <v>1752.754010958923</v>
+        <v>2239.359827154422</v>
       </c>
       <c r="T42" t="n">
-        <v>1540.271419830121</v>
+        <v>2026.87723602562</v>
       </c>
       <c r="U42" t="n">
-        <v>1332.988228153165</v>
+        <v>1819.594044348664</v>
       </c>
       <c r="V42" t="n">
-        <v>1111.260281495063</v>
+        <v>1597.866097690563</v>
       </c>
       <c r="W42" t="n">
-        <v>1111.133879300546</v>
+        <v>1597.866097690563</v>
       </c>
       <c r="X42" t="n">
-        <v>883.9997990526801</v>
+        <v>1370.732017442696</v>
       </c>
       <c r="Y42" t="n">
-        <v>677.5438467636556</v>
+        <v>1164.276065153672</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>96.43224858749356</v>
+        <v>101.7087580764521</v>
       </c>
       <c r="C43" t="n">
-        <v>96.43224858749356</v>
+        <v>101.7087580764521</v>
       </c>
       <c r="D43" t="n">
-        <v>96.43224858749356</v>
+        <v>101.7087580764521</v>
       </c>
       <c r="E43" t="n">
-        <v>96.43224858749356</v>
+        <v>101.7087580764521</v>
       </c>
       <c r="F43" t="n">
-        <v>96.43224858749356</v>
+        <v>101.7087580764521</v>
       </c>
       <c r="G43" t="n">
-        <v>96.43224858749356</v>
+        <v>101.7087580764521</v>
       </c>
       <c r="H43" t="n">
+        <v>67.59650948895853</v>
+      </c>
+      <c r="I43" t="n">
+        <v>67.59650948895853</v>
+      </c>
+      <c r="J43" t="n">
+        <v>77.49632980430073</v>
+      </c>
+      <c r="K43" t="n">
+        <v>77.49632980430073</v>
+      </c>
+      <c r="L43" t="n">
+        <v>77.49632980430073</v>
+      </c>
+      <c r="M43" t="n">
+        <v>77.49632980430073</v>
+      </c>
+      <c r="N43" t="n">
+        <v>77.49632980430073</v>
+      </c>
+      <c r="O43" t="n">
+        <v>77.49632980430073</v>
+      </c>
+      <c r="P43" t="n">
+        <v>77.49632980430073</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>77.49632980430073</v>
+      </c>
+      <c r="R43" t="n">
+        <v>77.49632980430073</v>
+      </c>
+      <c r="S43" t="n">
+        <v>77.49632980430073</v>
+      </c>
+      <c r="T43" t="n">
         <v>62.32</v>
       </c>
-      <c r="I43" t="n">
-        <v>80.50287893608291</v>
-      </c>
-      <c r="J43" t="n">
-        <v>238.6366195885342</v>
-      </c>
-      <c r="K43" t="n">
-        <v>238.6366195885342</v>
-      </c>
-      <c r="L43" t="n">
-        <v>238.6366195885342</v>
-      </c>
-      <c r="M43" t="n">
-        <v>238.6366195885342</v>
-      </c>
-      <c r="N43" t="n">
-        <v>99.6970926612952</v>
-      </c>
-      <c r="O43" t="n">
-        <v>99.6970926612952</v>
-      </c>
-      <c r="P43" t="n">
-        <v>99.6970926612952</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>99.6970926612952</v>
-      </c>
-      <c r="R43" t="n">
-        <v>99.6970926612952</v>
-      </c>
-      <c r="S43" t="n">
-        <v>99.6970926612952</v>
-      </c>
-      <c r="T43" t="n">
-        <v>84.52076285699448</v>
-      </c>
       <c r="U43" t="n">
-        <v>128.1219554952811</v>
+        <v>105.9211926382866</v>
       </c>
       <c r="V43" t="n">
-        <v>128.1219554952811</v>
+        <v>101.7087580764521</v>
       </c>
       <c r="W43" t="n">
-        <v>96.43224858749356</v>
+        <v>101.7087580764521</v>
       </c>
       <c r="X43" t="n">
-        <v>96.43224858749356</v>
+        <v>101.7087580764521</v>
       </c>
       <c r="Y43" t="n">
-        <v>96.43224858749356</v>
+        <v>101.7087580764521</v>
       </c>
     </row>
     <row r="44">
@@ -7615,25 +7615,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>945.1342997321999</v>
+        <v>692.0472465919817</v>
       </c>
       <c r="C44" t="n">
-        <v>945.1342997321999</v>
+        <v>692.0472465919817</v>
       </c>
       <c r="D44" t="n">
-        <v>646.811920196998</v>
+        <v>393.7248670567798</v>
       </c>
       <c r="E44" t="n">
-        <v>646.811920196998</v>
+        <v>393.7248670567798</v>
       </c>
       <c r="F44" t="n">
-        <v>353.9941134212285</v>
+        <v>393.7248670567798</v>
       </c>
       <c r="G44" t="n">
-        <v>62.32</v>
+        <v>393.7248670567798</v>
       </c>
       <c r="H44" t="n">
-        <v>62.32</v>
+        <v>97.75551483099457</v>
       </c>
       <c r="I44" t="n">
         <v>62.32</v>
@@ -7645,13 +7645,13 @@
         <v>1163.335479385524</v>
       </c>
       <c r="L44" t="n">
-        <v>1934.545479385524</v>
+        <v>1163.335479385524</v>
       </c>
       <c r="M44" t="n">
-        <v>2064.180585172569</v>
+        <v>1674.184308114459</v>
       </c>
       <c r="N44" t="n">
-        <v>2677.400904947332</v>
+        <v>2287.404627889222</v>
       </c>
       <c r="O44" t="n">
         <v>2677.400904947332</v>
@@ -7666,25 +7666,25 @@
         <v>3116</v>
       </c>
       <c r="S44" t="n">
-        <v>2732.314982017856</v>
+        <v>3070.008083251151</v>
       </c>
       <c r="T44" t="n">
-        <v>2486.906172637354</v>
+        <v>2593.568101707147</v>
       </c>
       <c r="U44" t="n">
-        <v>1947.288701376131</v>
+        <v>2593.568101707147</v>
       </c>
       <c r="V44" t="n">
-        <v>1427.237161813682</v>
+        <v>2073.516562144699</v>
       </c>
       <c r="W44" t="n">
-        <v>1427.237161813682</v>
+        <v>1544.856485396267</v>
       </c>
       <c r="X44" t="n">
-        <v>945.1342997321999</v>
+        <v>1062.753623314784</v>
       </c>
       <c r="Y44" t="n">
-        <v>945.1342997321999</v>
+        <v>1062.753623314784</v>
       </c>
     </row>
     <row r="45">
@@ -7718,22 +7718,22 @@
         <v>62.32</v>
       </c>
       <c r="J45" t="n">
-        <v>286.8069394125355</v>
+        <v>300.126520175299</v>
       </c>
       <c r="K45" t="n">
-        <v>589.8497555069189</v>
+        <v>603.1693362696824</v>
       </c>
       <c r="L45" t="n">
-        <v>975.0502171021189</v>
+        <v>975.0502171021192</v>
       </c>
       <c r="M45" t="n">
-        <v>1174.980758844978</v>
+        <v>1061.130758844978</v>
       </c>
       <c r="N45" t="n">
-        <v>1422.111043452546</v>
+        <v>1308.261043452547</v>
       </c>
       <c r="O45" t="n">
-        <v>1775.003495136265</v>
+        <v>1661.153495136266</v>
       </c>
       <c r="P45" t="n">
         <v>1887.532839605772</v>
@@ -7742,28 +7742,28 @@
         <v>1887.532839605772</v>
       </c>
       <c r="R45" t="n">
-        <v>1619.325261012382</v>
+        <v>1887.532839605772</v>
       </c>
       <c r="S45" t="n">
-        <v>1619.325261012382</v>
+        <v>1887.532839605772</v>
       </c>
       <c r="T45" t="n">
-        <v>1326.0345890755</v>
+        <v>1887.532839605772</v>
       </c>
       <c r="U45" t="n">
-        <v>1037.943316590462</v>
+        <v>1887.532839605772</v>
       </c>
       <c r="V45" t="n">
-        <v>1037.943316590462</v>
+        <v>1618.164827794214</v>
       </c>
       <c r="W45" t="n">
-        <v>1037.943316590462</v>
+        <v>1618.164827794214</v>
       </c>
       <c r="X45" t="n">
-        <v>1037.943316590462</v>
+        <v>1310.222666738267</v>
       </c>
       <c r="Y45" t="n">
-        <v>750.6792834933572</v>
+        <v>1022.958633641162</v>
       </c>
     </row>
     <row r="46">
@@ -7964,28 +7964,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>67.48000624509041</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L2" t="n">
-        <v>477.884502749055</v>
+        <v>815</v>
       </c>
       <c r="M2" t="n">
-        <v>1060.271045550332</v>
+        <v>651.0592759120859</v>
       </c>
       <c r="N2" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O2" t="n">
-        <v>885.2478695740924</v>
+        <v>70.24786957409242</v>
       </c>
       <c r="P2" t="n">
         <v>815.2870600406815</v>
       </c>
       <c r="Q2" t="n">
-        <v>189.0411843274853</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,19 +8201,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>51.26150624509023</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K5" t="n">
-        <v>16.21850000000013</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>51.07361380696587</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N5" t="n">
-        <v>1096.663422488788</v>
+        <v>784.9123059546883</v>
       </c>
       <c r="O5" t="n">
         <v>885.2478695740924</v>
@@ -8438,25 +8438,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>51.26150624509023</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K8" t="n">
-        <v>15.58188507602176</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N8" t="n">
-        <v>477.2489580698364</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O8" t="n">
         <v>885.2478695740924</v>
       </c>
       <c r="P8" t="n">
-        <v>671.4117531905774</v>
+        <v>503.5359435065815</v>
       </c>
       <c r="Q8" t="n">
         <v>615.8520732695737</v>
@@ -8675,10 +8675,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>18.61793580165096</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -8690,10 +8690,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O11" t="n">
-        <v>885.2478695740924</v>
+        <v>606.7289575115773</v>
       </c>
       <c r="P11" t="n">
-        <v>815.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
         <v>615.8520732695737</v>
@@ -8912,28 +8912,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L14" t="n">
-        <v>814.9999999999999</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N14" t="n">
-        <v>1096.663422488788</v>
+        <v>818.1445104262727</v>
       </c>
       <c r="O14" t="n">
-        <v>70.24786957409245</v>
+        <v>885.2478695740924</v>
       </c>
       <c r="P14" t="n">
-        <v>560.0592672613216</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q14" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,10 +9149,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>18.61793580165106</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L17" t="n">
         <v>815</v>
@@ -9161,16 +9161,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O17" t="n">
-        <v>885.2478695740924</v>
+        <v>854.1728108726184</v>
       </c>
       <c r="P17" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,13 +9386,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>461.6473247437395</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>536.481087937485</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
@@ -9401,13 +9401,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O20" t="n">
-        <v>885.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P20" t="n">
-        <v>815.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q20" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,25 +9623,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L23" t="n">
-        <v>632.7517361865667</v>
+        <v>815</v>
       </c>
       <c r="M23" t="n">
         <v>544.2621276423173</v>
       </c>
       <c r="N23" t="n">
-        <v>1096.663422488788</v>
+        <v>519.1534283342882</v>
       </c>
       <c r="O23" t="n">
-        <v>70.24786957409245</v>
+        <v>885.2478695740924</v>
       </c>
       <c r="P23" t="n">
-        <v>815.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q23" t="n">
         <v>615.8520732695737</v>
@@ -9860,28 +9860,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>430.3047365861567</v>
+        <v>225.2786768282658</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
-        <v>172.225215334032</v>
+        <v>779</v>
       </c>
       <c r="M26" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N26" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
         <v>849.2478695741179</v>
       </c>
       <c r="P26" t="n">
-        <v>779.2870600407069</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q26" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10100,7 +10100,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -10109,13 +10109,13 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N29" t="n">
-        <v>649.4741734038535</v>
+        <v>711.5990558807861</v>
       </c>
       <c r="O29" t="n">
         <v>849.2478695741245</v>
       </c>
       <c r="P29" t="n">
-        <v>779.2870600407135</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q29" t="n">
         <v>615.8520732695737</v>
@@ -10337,19 +10337,19 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L32" t="n">
-        <v>69.79098661544376</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>544.2621276423173</v>
+        <v>676.1779967347078</v>
       </c>
       <c r="N32" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O32" t="n">
-        <v>849.2478695741381</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P32" t="n">
         <v>779.2870600407272</v>
@@ -10577,22 +10577,22 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L35" t="n">
-        <v>574.9452580344541</v>
+        <v>394.9069511844207</v>
       </c>
       <c r="M35" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O35" t="n">
-        <v>849.2478695741627</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P35" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10811,22 +10811,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L38" t="n">
-        <v>778.9999999999997</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O38" t="n">
-        <v>243.4444027004815</v>
+        <v>22.40924803820286</v>
       </c>
       <c r="P38" t="n">
-        <v>779.2870600407717</v>
+        <v>443.0326327612391</v>
       </c>
       <c r="Q38" t="n">
         <v>615.8520732695737</v>
@@ -11048,10 +11048,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L41" t="n">
-        <v>779</v>
+        <v>750.3590157188617</v>
       </c>
       <c r="M41" t="n">
         <v>544.2621276423173</v>
@@ -11060,7 +11060,7 @@
         <v>477.2489580698352</v>
       </c>
       <c r="O41" t="n">
-        <v>758.4820028160536</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P41" t="n">
         <v>779.2870600408181</v>
@@ -11288,16 +11288,16 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>779</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>675.2066789423629</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O44" t="n">
-        <v>70.24786957409245</v>
+        <v>464.1835029661229</v>
       </c>
       <c r="P44" t="n">
         <v>0.2870600406814136</v>
@@ -23223,25 +23223,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>256.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>71.69129797697082</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>168.8679551544193</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23274,13 +23274,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>269.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>424.2212965486107</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -23390,7 +23390,7 @@
         <v>60.53621805555548</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>55.98090483695654</v>
       </c>
       <c r="F13" t="n">
         <v>49.38285596774193</v>
@@ -23399,7 +23399,7 @@
         <v>20.04387284153003</v>
       </c>
       <c r="H13" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -23426,10 +23426,10 @@
         <v>462.4478973282775</v>
       </c>
       <c r="Q13" t="n">
-        <v>500.839266425598</v>
+        <v>158.6896570983606</v>
       </c>
       <c r="R13" t="n">
-        <v>274.127650238714</v>
+        <v>501.6021279811511</v>
       </c>
       <c r="S13" t="n">
         <v>137.3734797028554</v>
@@ -23450,7 +23450,7 @@
         <v>22.44364543010755</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>62.46535284946236</v>
       </c>
     </row>
     <row r="14">
@@ -23618,7 +23618,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>8.113800337078658</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -23645,16 +23645,16 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>9.520773801143037</v>
       </c>
       <c r="L16" t="n">
-        <v>144.5476281577792</v>
+        <v>130.9139514623599</v>
       </c>
       <c r="M16" t="n">
-        <v>221.2778458610942</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>292.1850752716849</v>
       </c>
       <c r="O16" t="n">
         <v>361.445564079015</v>
@@ -23669,7 +23669,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>83.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23687,7 +23687,7 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>8.465352849462363</v>
       </c>
     </row>
     <row r="17">
@@ -23861,7 +23861,7 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>6.53621805555548</v>
       </c>
       <c r="E19" t="n">
         <v>1.98090483695654</v>
@@ -23894,16 +23894,16 @@
         <v>292.1850752716849</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>361.445564079015</v>
       </c>
       <c r="P19" t="n">
-        <v>82.0276162331898</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q19" t="n">
-        <v>446.839266425598</v>
+        <v>191.5739783276288</v>
       </c>
       <c r="R19" t="n">
-        <v>447.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -23924,7 +23924,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>8.465352849462363</v>
       </c>
     </row>
     <row r="20">
@@ -24092,16 +24092,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8.113800337078658</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>6.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>1.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -24119,25 +24119,25 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>9.520773801143037</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>144.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>241.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>292.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>361.445564079015</v>
+        <v>288.1860330092492</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q22" t="n">
-        <v>77.51162082136204</v>
+        <v>446.839266425598</v>
       </c>
       <c r="R22" t="n">
         <v>447.6021279811511</v>
@@ -24356,16 +24356,16 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>9.520773801143037</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>144.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>203.6950417659222</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>292.1850752716849</v>
       </c>
       <c r="O25" t="n">
         <v>361.445564079015</v>
@@ -24377,7 +24377,7 @@
         <v>446.839266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>65.57836845315933</v>
       </c>
       <c r="S25" t="n">
         <v>83.37347970285543</v>
@@ -24408,13 +24408,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>256.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>224.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -24423,10 +24423,10 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>120.7049404717253</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24462,7 +24462,7 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>361.6755817285639</v>
+        <v>222.0060407772299</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -24477,7 +24477,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>286.3174326828064</v>
       </c>
     </row>
     <row r="27">
@@ -24584,7 +24584,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -24593,19 +24593,19 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>63.52077380114304</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>198.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>295.6316114025499</v>
+        <v>235.5942768757648</v>
       </c>
       <c r="N28" t="n">
         <v>346.1850752716849</v>
       </c>
       <c r="O28" t="n">
-        <v>89.56870149168907</v>
+        <v>415.445564079015</v>
       </c>
       <c r="P28" t="n">
         <v>462.4478973282775</v>
@@ -24648,13 +24648,13 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>198.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -24696,7 +24696,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>243.8481678023229</v>
+        <v>114.5778863249107</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -24705,7 +24705,7 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>85.93586256926858</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -24714,7 +24714,7 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>260.3174326828064</v>
       </c>
     </row>
     <row r="30">
@@ -24833,7 +24833,7 @@
         <v>37.52077380114304</v>
       </c>
       <c r="L31" t="n">
-        <v>80.41497833034852</v>
+        <v>172.5476281577792</v>
       </c>
       <c r="M31" t="n">
         <v>269.6316114025499</v>
@@ -24842,7 +24842,7 @@
         <v>320.1850752716849</v>
       </c>
       <c r="O31" t="n">
-        <v>389.445564079015</v>
+        <v>297.3129142515843</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -24885,7 +24885,7 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>10.25860861458554</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -24939,7 +24939,7 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>10.25860861458591</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -25067,31 +25067,31 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0.5207738011430365</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>135.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>232.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>283.1850752716849</v>
+        <v>196.5296810174123</v>
       </c>
       <c r="O34" t="n">
         <v>352.445564079015</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>399.4478973282775</v>
       </c>
       <c r="Q34" t="n">
         <v>437.839266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>18.46596941538814</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>74.37347970285543</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25125,7 +25125,7 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>10.2586086145855</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -25173,7 +25173,7 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>10.25860861458551</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -25310,25 +25310,25 @@
         <v>135.5476281577792</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>232.6316114025499</v>
       </c>
       <c r="N37" t="n">
-        <v>283.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>204.0952475686756</v>
+        <v>141.1210010820815</v>
       </c>
       <c r="P37" t="n">
-        <v>399.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>437.839266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>438.6021279811511</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>74.37347970285543</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25407,7 +25407,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>10.25860861422103</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -25425,7 +25425,7 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>10.25860861457684</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -25541,7 +25541,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>0.5207738011430365</v>
       </c>
       <c r="L40" t="n">
         <v>135.5476281577792</v>
@@ -25556,13 +25556,13 @@
         <v>352.445564079015</v>
       </c>
       <c r="P40" t="n">
-        <v>18.22388166097812</v>
+        <v>399.4478973282775</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>56.85733851270868</v>
       </c>
       <c r="R40" t="n">
-        <v>438.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -25599,7 +25599,7 @@
         <v>254.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>215.3391557398498</v>
       </c>
       <c r="E41" t="n">
         <v>209.3632896068686</v>
@@ -25608,7 +25608,7 @@
         <v>209.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>208.7573722870162</v>
       </c>
       <c r="H41" t="n">
         <v>213.0096587035274</v>
@@ -25644,7 +25644,7 @@
         <v>55.87859882829446</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>1.42492532631735</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -25656,13 +25656,13 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>109.204020670377</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>316.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -25672,7 +25672,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>189.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -25681,10 +25681,10 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>147.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>144.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -25720,10 +25720,10 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>116.9195516837676</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>271.5639999646113</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
@@ -25735,7 +25735,7 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>237.2480047372568</v>
+        <v>237.3731429098285</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -25787,7 +25787,7 @@
         <v>325.6316114025499</v>
       </c>
       <c r="N43" t="n">
-        <v>238.6349436137183</v>
+        <v>376.1850752716849</v>
       </c>
       <c r="O43" t="n">
         <v>445.445564079015</v>
@@ -25811,10 +25811,10 @@
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>4.170310216216194</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>31.37280983870968</v>
       </c>
       <c r="X43" t="n">
         <v>52.44364543010755</v>
@@ -25830,7 +25830,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>366.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
         <v>334.4745782429939</v>
@@ -25842,16 +25842,16 @@
         <v>289.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>289.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>288.7573722870162</v>
       </c>
       <c r="H44" t="n">
-        <v>293.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>35.08115968268461</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -25881,19 +25881,19 @@
         <v>135.8785988282945</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>334.3161702209621</v>
       </c>
       <c r="T44" t="n">
-        <v>228.7208604418672</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>534.2212965486107</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>523.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
@@ -25909,7 +25909,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>269.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -25957,25 +25957,25 @@
         <v>58.07926509047959</v>
       </c>
       <c r="R45" t="n">
-        <v>166.7482944849233</v>
+        <v>432.2737972923793</v>
       </c>
       <c r="S45" t="n">
         <v>351.5639999646113</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>290.3577652175138</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>285.2103597601867</v>
       </c>
       <c r="V45" t="n">
-        <v>299.5106671915202</v>
+        <v>32.83633549807814</v>
       </c>
       <c r="W45" t="n">
         <v>317.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>304.8627394453875</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
         <v>0</v>
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3816781.761264503</v>
+        <v>3816781.761264505</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4731174.463033903</v>
+        <v>4731174.463033904</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5645567.1648033</v>
+        <v>5645567.164803298</v>
       </c>
     </row>
     <row r="8">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7474352.568342086</v>
+        <v>7474352.568342085</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8307645.083917885</v>
+        <v>8307645.083917881</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9178498.914630629</v>
+        <v>9178498.914630624</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10096149.0720983</v>
+        <v>10096149.07209829</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11013777.96741951</v>
+        <v>11013777.9674195</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11931406.86274071</v>
+        <v>11931406.86274073</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12705152.5003152</v>
+        <v>12705152.50031522</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13311123.61064594</v>
+        <v>13311123.61064596</v>
       </c>
     </row>
   </sheetData>
@@ -26275,7 +26275,7 @@
         <v>1259377.040332595</v>
       </c>
       <c r="D2" t="n">
-        <v>1259377.040332595</v>
+        <v>1259377.040332594</v>
       </c>
       <c r="E2" t="n">
         <v>1126337.93458107</v>
@@ -26284,10 +26284,10 @@
         <v>1219190.269025864</v>
       </c>
       <c r="G2" t="n">
-        <v>1219190.269025865</v>
+        <v>1219190.269025864</v>
       </c>
       <c r="H2" t="n">
-        <v>1219190.269025865</v>
+        <v>1219190.269025864</v>
       </c>
       <c r="I2" t="n">
         <v>1219190.269025864</v>
@@ -26302,10 +26302,10 @@
         <v>1223505.193761598</v>
       </c>
       <c r="M2" t="n">
-        <v>1223505.193761598</v>
+        <v>1223505.193761599</v>
       </c>
       <c r="N2" t="n">
-        <v>1223505.193761599</v>
+        <v>1223505.193761627</v>
       </c>
       <c r="O2" t="n">
         <v>1031689.199627948</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>575920.3474495772</v>
+        <v>580809.5038374889</v>
       </c>
       <c r="C4" t="n">
-        <v>574167.5049491362</v>
+        <v>579056.661337048</v>
       </c>
       <c r="D4" t="n">
-        <v>572412.2846084387</v>
+        <v>577301.4409963507</v>
       </c>
       <c r="E4" t="n">
-        <v>493973.8046613694</v>
+        <v>498813.3005071199</v>
       </c>
       <c r="F4" t="n">
-        <v>544553.6268564411</v>
+        <v>549393.1227021916</v>
       </c>
       <c r="G4" t="n">
-        <v>542883.645165896</v>
+        <v>547723.1410116465</v>
       </c>
       <c r="H4" t="n">
-        <v>541211.3456360602</v>
+        <v>546050.8414818107</v>
       </c>
       <c r="I4" t="n">
-        <v>539536.7115489381</v>
+        <v>544376.2073946884</v>
       </c>
       <c r="J4" t="n">
-        <v>483585.363292172</v>
+        <v>488315.773108913</v>
       </c>
       <c r="K4" t="n">
-        <v>507320.6786559278</v>
+        <v>512051.0884726688</v>
       </c>
       <c r="L4" t="n">
-        <v>539876.9064614967</v>
+        <v>544608.0596004378</v>
       </c>
       <c r="M4" t="n">
-        <v>538156.9451324799</v>
+        <v>542888.098271421</v>
       </c>
       <c r="N4" t="n">
-        <v>536434.5107850768</v>
+        <v>541165.6639240405</v>
       </c>
       <c r="O4" t="n">
-        <v>430730.7840429268</v>
+        <v>435461.1938596679</v>
       </c>
       <c r="P4" t="n">
-        <v>308208.0261529455</v>
+        <v>312938.4359696866</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>313397.092883018</v>
+        <v>308507.9364951064</v>
       </c>
       <c r="C6" t="n">
-        <v>602029.935383459</v>
+        <v>597140.7789955466</v>
       </c>
       <c r="D6" t="n">
-        <v>603785.1557241566</v>
+        <v>598895.9993362437</v>
       </c>
       <c r="E6" t="n">
-        <v>383896.6049197008</v>
+        <v>379057.1090739503</v>
       </c>
       <c r="F6" t="n">
-        <v>558429.3911694231</v>
+        <v>553589.8953236727</v>
       </c>
       <c r="G6" t="n">
-        <v>603299.3728599685</v>
+        <v>598459.8770142173</v>
       </c>
       <c r="H6" t="n">
-        <v>604971.6723898043</v>
+        <v>600132.1765440536</v>
       </c>
       <c r="I6" t="n">
-        <v>606646.3064769262</v>
+        <v>601806.8106311756</v>
       </c>
       <c r="J6" t="n">
-        <v>154345.0258088978</v>
+        <v>149614.6159921572</v>
       </c>
       <c r="K6" t="n">
-        <v>521353.2432944056</v>
+        <v>516622.8334776644</v>
       </c>
       <c r="L6" t="n">
-        <v>582453.2153001016</v>
+        <v>577722.0621611605</v>
       </c>
       <c r="M6" t="n">
-        <v>613773.1766291182</v>
+        <v>609042.0234901775</v>
       </c>
       <c r="N6" t="n">
-        <v>615495.6109765224</v>
+        <v>610764.4578375869</v>
       </c>
       <c r="O6" t="n">
-        <v>474801.7605850215</v>
+        <v>470071.3507682804</v>
       </c>
       <c r="P6" t="n">
-        <v>442722.3192880293</v>
+        <v>437991.9094712882</v>
       </c>
     </row>
   </sheetData>
@@ -26975,7 +26975,7 @@
         <v>-0</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D2" t="n">
         <v>-0</v>
@@ -26987,13 +26987,13 @@
         <v>54</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>171</v>
@@ -27005,7 +27005,7 @@
         <v>37</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>-0</v>
@@ -27439,7 +27439,7 @@
         <v>400</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E2" t="n">
         <v>400</v>
@@ -27448,49 +27448,49 @@
         <v>400</v>
       </c>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>303.5095671255643</v>
+      </c>
+      <c r="U2" t="n">
         <v>400</v>
-      </c>
-      <c r="H2" t="n">
-        <v>400</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>250.8785988282945</v>
-      </c>
-      <c r="S2" t="n">
-        <v>400</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>52.63096829727021</v>
       </c>
       <c r="V2" t="n">
         <v>400</v>
@@ -27499,7 +27499,7 @@
         <v>400</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y2" t="n">
         <v>400</v>
@@ -27524,7 +27524,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>271.5076617024168</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
         <v>325.7395358750273</v>
@@ -27533,7 +27533,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27569,10 +27569,10 @@
         <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>400</v>
+        <v>115.353640707057</v>
       </c>
       <c r="V3" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>400</v>
@@ -27581,7 +27581,7 @@
         <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="4">
@@ -27594,7 +27594,7 @@
         <v>400</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D4" t="n">
         <v>285.5362180555555</v>
@@ -27603,10 +27603,10 @@
         <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
-        <v>300.2295135175848</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H4" t="n">
         <v>400</v>
@@ -27615,10 +27615,10 @@
         <v>176.6334556201183</v>
       </c>
       <c r="J4" t="n">
-        <v>400</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27645,16 +27645,16 @@
         <v>362.3734797028554</v>
       </c>
       <c r="T4" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9583912744579</v>
+        <v>317.0940763387322</v>
       </c>
       <c r="V4" t="n">
         <v>400</v>
       </c>
       <c r="W4" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X4" t="n">
         <v>400</v>
@@ -27679,10 +27679,10 @@
         <v>400</v>
       </c>
       <c r="E5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>400</v>
@@ -27724,22 +27724,22 @@
         <v>400</v>
       </c>
       <c r="T5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>52.63096829726976</v>
       </c>
       <c r="V5" t="n">
         <v>400</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="X5" t="n">
-        <v>52.6309682972701</v>
+        <v>400</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6">
@@ -27749,16 +27749,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>217.4407163825192</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>193.9840721817118</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
@@ -27831,25 +27831,25 @@
         <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>305.756406482019</v>
+        <v>400</v>
       </c>
       <c r="D7" t="n">
         <v>400</v>
       </c>
       <c r="E7" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F7" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G7" t="n">
+        <v>245.04387284153</v>
+      </c>
+      <c r="H7" t="n">
+        <v>323.6339786265217</v>
+      </c>
+      <c r="I7" t="n">
         <v>400</v>
-      </c>
-      <c r="F7" t="n">
-        <v>400</v>
-      </c>
-      <c r="G7" t="n">
-        <v>400</v>
-      </c>
-      <c r="H7" t="n">
-        <v>228.7711261016186</v>
-      </c>
-      <c r="I7" t="n">
-        <v>176.6334556201183</v>
       </c>
       <c r="J7" t="n">
         <v>35.26894883590776</v>
@@ -27885,19 +27885,19 @@
         <v>400</v>
       </c>
       <c r="U7" t="n">
-        <v>150.9583912744579</v>
+        <v>400</v>
       </c>
       <c r="V7" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
         <v>400</v>
       </c>
       <c r="Y7" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -27910,16 +27910,16 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>302.5498086145857</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>400</v>
       </c>
       <c r="E8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>400</v>
@@ -27958,16 +27958,16 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S8" t="n">
-        <v>400</v>
+        <v>302.5498086145854</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="W8" t="n">
         <v>400</v>
@@ -27976,7 +27976,7 @@
         <v>400</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -28007,7 +28007,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28034,10 +28034,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
-        <v>159.4007615079257</v>
+        <v>342.2743756165773</v>
       </c>
       <c r="S9" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
         <v>400</v>
@@ -28065,28 +28065,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C10" t="n">
         <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E10" t="n">
         <v>400</v>
       </c>
       <c r="F10" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G10" t="n">
+        <v>245.04387284153</v>
+      </c>
+      <c r="H10" t="n">
         <v>400</v>
       </c>
-      <c r="G10" t="n">
-        <v>400</v>
-      </c>
-      <c r="H10" t="n">
-        <v>228.7711261016186</v>
-      </c>
       <c r="I10" t="n">
-        <v>400</v>
+        <v>191.734259394484</v>
       </c>
       <c r="J10" t="n">
         <v>35.26894883590776</v>
@@ -28125,16 +28125,16 @@
         <v>150.9583912744579</v>
       </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W10" t="n">
         <v>400</v>
       </c>
       <c r="X10" t="n">
-        <v>398.0348863427491</v>
+        <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28244,7 +28244,7 @@
         <v>225</v>
       </c>
       <c r="I12" t="n">
-        <v>217.1263858913485</v>
+        <v>225</v>
       </c>
       <c r="J12" t="n">
         <v>225</v>
@@ -28253,7 +28253,7 @@
         <v>225</v>
       </c>
       <c r="L12" t="n">
-        <v>26.99048536749075</v>
+        <v>19.11687125883935</v>
       </c>
       <c r="M12" t="n">
         <v>225</v>
@@ -28402,7 +28402,7 @@
         <v>279</v>
       </c>
       <c r="I14" t="n">
-        <v>150.0811596826846</v>
+        <v>146.6309682972706</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28429,7 +28429,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>247.42840744288</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S14" t="n">
         <v>279</v>
@@ -28481,31 +28481,31 @@
         <v>279</v>
       </c>
       <c r="I15" t="n">
-        <v>217.1263858913485</v>
+        <v>279</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>155.6705902671029</v>
+      </c>
+      <c r="O15" t="n">
         <v>279</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>279</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>44.46493928527505</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>173.0792650904796</v>
       </c>
       <c r="R15" t="n">
         <v>279</v>
@@ -28633,13 +28633,13 @@
         <v>279</v>
       </c>
       <c r="G17" t="n">
-        <v>279</v>
+        <v>275.549808614586</v>
       </c>
       <c r="H17" t="n">
         <v>279</v>
       </c>
       <c r="I17" t="n">
-        <v>146.6309682972706</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28718,31 +28718,31 @@
         <v>279</v>
       </c>
       <c r="I18" t="n">
-        <v>217.1263858913485</v>
+        <v>279</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>155.6705902671029</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
         <v>279</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>279</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>217.5442043757548</v>
       </c>
       <c r="R18" t="n">
         <v>279</v>
@@ -28955,17 +28955,17 @@
         <v>279</v>
       </c>
       <c r="I21" t="n">
-        <v>217.1263858913485</v>
+        <v>279</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
+        <v>155.670590267103</v>
+      </c>
+      <c r="L21" t="n">
         <v>279</v>
       </c>
-      <c r="L21" t="n">
-        <v>44.46493928527474</v>
-      </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
@@ -28976,10 +28976,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>279</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>173.0792650904796</v>
       </c>
       <c r="R21" t="n">
         <v>279</v>
@@ -29113,7 +29113,7 @@
         <v>279</v>
       </c>
       <c r="I23" t="n">
-        <v>146.6309682972706</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>250.8785988282945</v>
+        <v>247.42840744288</v>
       </c>
       <c r="S23" t="n">
         <v>279</v>
@@ -29192,31 +29192,31 @@
         <v>279</v>
       </c>
       <c r="I24" t="n">
-        <v>217.1263858913485</v>
+        <v>279</v>
       </c>
       <c r="J24" t="n">
-        <v>44.46493928527471</v>
+        <v>279</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>155.6705902671031</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>279</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>279</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>173.0792650904796</v>
       </c>
       <c r="R24" t="n">
         <v>279</v>
@@ -29429,10 +29429,10 @@
         <v>225</v>
       </c>
       <c r="I27" t="n">
-        <v>217.1263858913485</v>
+        <v>225</v>
       </c>
       <c r="J27" t="n">
-        <v>26.99048536749066</v>
+        <v>225</v>
       </c>
       <c r="K27" t="n">
         <v>225</v>
@@ -29447,7 +29447,7 @@
         <v>225</v>
       </c>
       <c r="O27" t="n">
-        <v>225</v>
+        <v>19.11687125883898</v>
       </c>
       <c r="P27" t="n">
         <v>225</v>
@@ -29669,28 +29669,28 @@
         <v>251</v>
       </c>
       <c r="J30" t="n">
-        <v>244.1190264315979</v>
+        <v>251</v>
       </c>
       <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
         <v>251</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>251</v>
       </c>
       <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>166.1982915220772</v>
+      </c>
+      <c r="Q30" t="n">
         <v>251</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>173.0792650904796</v>
       </c>
       <c r="R30" t="n">
         <v>251</v>
@@ -29903,7 +29903,7 @@
         <v>288</v>
       </c>
       <c r="I33" t="n">
-        <v>217.1263858913485</v>
+        <v>278.9295434351469</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29912,7 +29912,7 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -29921,10 +29921,10 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>61.80315754379858</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>288</v>
@@ -30140,10 +30140,10 @@
         <v>288</v>
       </c>
       <c r="I36" t="n">
-        <v>278.929543435147</v>
+        <v>288</v>
       </c>
       <c r="J36" t="n">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -30152,7 +30152,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>278.9295434351469</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -30292,7 +30292,7 @@
         <v>288</v>
       </c>
       <c r="G38" t="n">
-        <v>288.0000000000088</v>
+        <v>288</v>
       </c>
       <c r="H38" t="n">
         <v>288</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>250.8785988282945</v>
+        <v>250.8785988286661</v>
       </c>
       <c r="S38" t="n">
         <v>288</v>
@@ -30377,7 +30377,7 @@
         <v>288</v>
       </c>
       <c r="I39" t="n">
-        <v>217.1263858913485</v>
+        <v>288</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30386,22 +30386,22 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>176.7238924533193</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>278.929543435147</v>
+      </c>
+      <c r="Q39" t="n">
         <v>288</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>173.0792650904796</v>
       </c>
       <c r="R39" t="n">
         <v>288</v>
@@ -30623,19 +30623,19 @@
         <v>195</v>
       </c>
       <c r="L42" t="n">
-        <v>179.9891436145826</v>
+        <v>195</v>
       </c>
       <c r="M42" t="n">
         <v>195</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="O42" t="n">
         <v>195</v>
       </c>
       <c r="P42" t="n">
-        <v>195</v>
+        <v>80.13882873361749</v>
       </c>
       <c r="Q42" t="n">
         <v>195</v>
@@ -30693,10 +30693,10 @@
         <v>195</v>
       </c>
       <c r="I43" t="n">
-        <v>195</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J43" t="n">
-        <v>195</v>
+        <v>45.2687673362534</v>
       </c>
       <c r="K43" t="n">
         <v>195</v>
@@ -30854,16 +30854,16 @@
         <v>115</v>
       </c>
       <c r="J45" t="n">
-        <v>101.5458780174107</v>
+        <v>115</v>
       </c>
       <c r="K45" t="n">
         <v>115</v>
       </c>
       <c r="L45" t="n">
-        <v>115</v>
+        <v>101.5458780174107</v>
       </c>
       <c r="M45" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
         <v>115</v>
@@ -30872,7 +30872,7 @@
         <v>115</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="Q45" t="n">
         <v>115</v>
@@ -34746,10 +34746,10 @@
         <v>815</v>
       </c>
       <c r="K2" t="n">
+        <v>783.0093003026038</v>
+      </c>
+      <c r="L2" t="n">
         <v>815</v>
-      </c>
-      <c r="L2" t="n">
-        <v>783.0093003026409</v>
       </c>
       <c r="M2" t="n">
         <v>815</v>
@@ -34880,7 +34880,7 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -34889,10 +34889,10 @@
         <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>55.18564067605476</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>171.2288738983814</v>
@@ -34901,10 +34901,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>364.7310511640923</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34931,16 +34931,16 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>166.1356850642742</v>
       </c>
       <c r="V4" t="n">
         <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
         <v>152.5563545698924</v>
@@ -34980,19 +34980,19 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>815</v>
+        <v>815.0000000000011</v>
       </c>
       <c r="K5" t="n">
         <v>815</v>
       </c>
       <c r="L5" t="n">
-        <v>783.0093003025873</v>
+        <v>783.0093003026252</v>
       </c>
       <c r="M5" t="n">
         <v>815</v>
       </c>
       <c r="N5" t="n">
-        <v>815.0000000000011</v>
+        <v>815</v>
       </c>
       <c r="O5" t="n">
         <v>815</v>
@@ -35117,25 +35117,25 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>33.03115983397431</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
         <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>94.86285252490308</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -35171,19 +35171,19 @@
         <v>189.9754334937423</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V7" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35220,16 +35220,16 @@
         <v>815</v>
       </c>
       <c r="K8" t="n">
-        <v>783.0093003025949</v>
+        <v>815</v>
       </c>
       <c r="L8" t="n">
-        <v>815</v>
+        <v>783.0093003026029</v>
       </c>
       <c r="M8" t="n">
         <v>815</v>
       </c>
       <c r="N8" t="n">
-        <v>815.0000000000011</v>
+        <v>815</v>
       </c>
       <c r="O8" t="n">
         <v>815</v>
@@ -35351,28 +35351,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
-        <v>223.3665443798817</v>
+        <v>15.10080377436569</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -35411,16 +35411,16 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
         <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
-        <v>150.5912409126416</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35454,10 +35454,10 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K11" t="n">
-        <v>18.61793580165096</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -35469,10 +35469,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O11" t="n">
-        <v>815</v>
+        <v>536.4810879374849</v>
       </c>
       <c r="P11" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>443.0293889420883</v>
@@ -35530,7 +35530,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>7.873614108651466</v>
       </c>
       <c r="J12" t="n">
         <v>350.2086062376757</v>
@@ -35539,7 +35539,7 @@
         <v>416.1038546407913</v>
       </c>
       <c r="L12" t="n">
-        <v>301.0818607161777</v>
+        <v>293.2082466075263</v>
       </c>
       <c r="M12" t="n">
         <v>311.9500421645043</v>
@@ -35691,28 +35691,28 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K14" t="n">
-        <v>716.8751175230994</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L14" t="n">
-        <v>814.9999999999999</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N14" t="n">
-        <v>619.4144644189528</v>
+        <v>340.8955523564375</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="P14" t="n">
-        <v>559.77220722064</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35767,31 +35767,31 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>61.87361410865147</v>
       </c>
       <c r="J15" t="n">
-        <v>404.2086062376757</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K15" t="n">
         <v>191.1038546407913</v>
       </c>
       <c r="L15" t="n">
-        <v>553.0913753486871</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M15" t="n">
         <v>86.95004216450428</v>
       </c>
       <c r="N15" t="n">
-        <v>134.6265501086548</v>
+        <v>290.2971403757577</v>
       </c>
       <c r="O15" t="n">
-        <v>285.9219611880214</v>
+        <v>520.4570219027464</v>
       </c>
       <c r="P15" t="n">
         <v>113.6660045146532</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>105.9207349095204</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35928,10 +35928,10 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
-        <v>18.61793580165106</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L17" t="n">
         <v>815</v>
@@ -35940,16 +35940,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N17" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>815</v>
+        <v>783.9249412985259</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36004,13 +36004,13 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>61.87361410865147</v>
       </c>
       <c r="J18" t="n">
         <v>125.2086062376757</v>
       </c>
       <c r="K18" t="n">
-        <v>470.1038546407913</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L18" t="n">
         <v>274.091375348687</v>
@@ -36019,16 +36019,16 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N18" t="n">
-        <v>134.6265501086548</v>
+        <v>290.2971403757577</v>
       </c>
       <c r="O18" t="n">
-        <v>520.4570219027464</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P18" t="n">
-        <v>113.6660045146532</v>
+        <v>392.6660045146532</v>
       </c>
       <c r="Q18" t="n">
-        <v>44.46493928527515</v>
+        <v>105.9207349095204</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -36165,13 +36165,13 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>461.6473247437395</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>536.481087937485</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
@@ -36180,13 +36180,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O20" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36241,16 +36241,16 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>61.87361410865147</v>
       </c>
       <c r="J21" t="n">
         <v>125.2086062376757</v>
       </c>
       <c r="K21" t="n">
-        <v>470.1038546407913</v>
+        <v>346.7744449078943</v>
       </c>
       <c r="L21" t="n">
-        <v>318.5563146339617</v>
+        <v>553.0913753486871</v>
       </c>
       <c r="M21" t="n">
         <v>86.95004216450428</v>
@@ -36262,10 +36262,10 @@
         <v>241.4570219027464</v>
       </c>
       <c r="P21" t="n">
-        <v>392.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>105.9207349095204</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36402,25 +36402,25 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
-        <v>716.8751175230994</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L23" t="n">
-        <v>632.7517361865667</v>
+        <v>815</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>619.4144644189528</v>
+        <v>41.9044702644529</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="P23" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>443.0293889420883</v>
@@ -36478,31 +36478,31 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>61.87361410865147</v>
       </c>
       <c r="J24" t="n">
-        <v>169.6735455229504</v>
+        <v>404.2086062376757</v>
       </c>
       <c r="K24" t="n">
         <v>191.1038546407913</v>
       </c>
       <c r="L24" t="n">
-        <v>274.091375348687</v>
+        <v>429.7619656157901</v>
       </c>
       <c r="M24" t="n">
         <v>86.95004216450428</v>
       </c>
       <c r="N24" t="n">
-        <v>413.6265501086548</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O24" t="n">
         <v>241.4570219027464</v>
       </c>
       <c r="P24" t="n">
-        <v>392.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>105.9207349095204</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36639,28 +36639,28 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>395.2617303410664</v>
+        <v>190.2356705831754</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
-        <v>172.225215334032</v>
+        <v>779</v>
       </c>
       <c r="M26" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O26" t="n">
         <v>779.0000000000255</v>
       </c>
       <c r="P26" t="n">
-        <v>779.0000000000255</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36715,10 +36715,10 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>7.873614108651466</v>
       </c>
       <c r="J27" t="n">
-        <v>152.1990916051664</v>
+        <v>350.2086062376757</v>
       </c>
       <c r="K27" t="n">
         <v>416.1038546407913</v>
@@ -36733,7 +36733,7 @@
         <v>359.6265501086548</v>
       </c>
       <c r="O27" t="n">
-        <v>466.4570219027464</v>
+        <v>260.5738931615854</v>
       </c>
       <c r="P27" t="n">
         <v>338.6660045146532</v>
@@ -36879,7 +36879,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -36888,13 +36888,13 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N29" t="n">
-        <v>172.2252153340183</v>
+        <v>234.3500978109508</v>
       </c>
       <c r="O29" t="n">
         <v>779.0000000000321</v>
       </c>
       <c r="P29" t="n">
-        <v>779.0000000000321</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>443.0293889420883</v>
@@ -36955,28 +36955,28 @@
         <v>33.87361410865147</v>
       </c>
       <c r="J30" t="n">
-        <v>369.3276326692737</v>
+        <v>376.2086062376757</v>
       </c>
       <c r="K30" t="n">
-        <v>442.1038546407913</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L30" t="n">
-        <v>274.091375348687</v>
+        <v>525.0913753486871</v>
       </c>
       <c r="M30" t="n">
         <v>337.9500421645043</v>
       </c>
       <c r="N30" t="n">
-        <v>385.6265501086548</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O30" t="n">
         <v>241.4570219027464</v>
       </c>
       <c r="P30" t="n">
-        <v>113.6660045146532</v>
+        <v>279.8642960367304</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>77.92073490952041</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -37116,19 +37116,19 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>764.7137390468334</v>
       </c>
       <c r="L32" t="n">
-        <v>117.6296081391455</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>131.9158690923905</v>
       </c>
       <c r="N32" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O32" t="n">
-        <v>779.0000000000457</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
         <v>779.0000000000457</v>
@@ -37189,7 +37189,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>61.80315754379833</v>
       </c>
       <c r="J33" t="n">
         <v>125.2086062376757</v>
@@ -37198,7 +37198,7 @@
         <v>191.1038546407913</v>
       </c>
       <c r="L33" t="n">
-        <v>274.091375348687</v>
+        <v>562.0913753486871</v>
       </c>
       <c r="M33" t="n">
         <v>86.95004216450428</v>
@@ -37207,10 +37207,10 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O33" t="n">
-        <v>529.4570219027464</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P33" t="n">
-        <v>175.4691620584518</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q33" t="n">
         <v>114.9207349095204</v>
@@ -37356,22 +37356,22 @@
         <v>716.8751175230996</v>
       </c>
       <c r="L35" t="n">
-        <v>622.7838795581545</v>
+        <v>442.7455727081267</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N35" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O35" t="n">
-        <v>779.0000000000703</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37426,10 +37426,10 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>61.80315754379851</v>
+        <v>70.87361410865147</v>
       </c>
       <c r="J36" t="n">
-        <v>413.2086062376757</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K36" t="n">
         <v>191.1038546407913</v>
@@ -37438,7 +37438,7 @@
         <v>274.091375348687</v>
       </c>
       <c r="M36" t="n">
-        <v>86.95004216450428</v>
+        <v>365.8795855996512</v>
       </c>
       <c r="N36" t="n">
         <v>134.6265501086548</v>
@@ -37590,28 +37590,28 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K38" t="n">
-        <v>47.8386215239999</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L38" t="n">
-        <v>778.9999999999999</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O38" t="n">
-        <v>173.196533126389</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>779.0000000000903</v>
+        <v>442.7455727205577</v>
       </c>
       <c r="Q38" t="n">
         <v>443.0293889420883</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>3.716066736031813e-10</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -37663,7 +37663,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>70.87361410865147</v>
       </c>
       <c r="J39" t="n">
         <v>125.2086062376757</v>
@@ -37672,22 +37672,22 @@
         <v>191.1038546407913</v>
       </c>
       <c r="L39" t="n">
-        <v>450.8152678020062</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M39" t="n">
         <v>86.95004216450428</v>
       </c>
       <c r="N39" t="n">
-        <v>422.6265501086548</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O39" t="n">
         <v>241.4570219027464</v>
       </c>
       <c r="P39" t="n">
-        <v>113.6660045146532</v>
+        <v>392.5955479498002</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>114.9207349095204</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37827,10 +37827,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L41" t="n">
-        <v>779</v>
+        <v>750.3590157188617</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -37839,7 +37839,7 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>688.2341332419612</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
         <v>779.0000000001367</v>
@@ -37909,19 +37909,19 @@
         <v>386.1038546407913</v>
       </c>
       <c r="L42" t="n">
-        <v>454.0805189632696</v>
+        <v>469.091375348687</v>
       </c>
       <c r="M42" t="n">
         <v>281.9500421645043</v>
       </c>
       <c r="N42" t="n">
-        <v>134.6265501086548</v>
+        <v>329.6265501086548</v>
       </c>
       <c r="O42" t="n">
         <v>436.4570219027464</v>
       </c>
       <c r="P42" t="n">
-        <v>308.6660045146532</v>
+        <v>193.8048332482707</v>
       </c>
       <c r="Q42" t="n">
         <v>21.92073490952041</v>
@@ -37979,10 +37979,10 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>18.36654437988173</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>159.7310511640922</v>
+        <v>9.999818500345654</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -38067,16 +38067,16 @@
         <v>716.8751175230996</v>
       </c>
       <c r="L44" t="n">
-        <v>779</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>130.9445513000456</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N44" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>393.9356333920304</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -38140,16 +38140,16 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>226.7544842550864</v>
+        <v>240.2086062376757</v>
       </c>
       <c r="K45" t="n">
         <v>306.1038546407913</v>
       </c>
       <c r="L45" t="n">
-        <v>389.091375348687</v>
+        <v>375.6372533660977</v>
       </c>
       <c r="M45" t="n">
-        <v>201.9500421645043</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N45" t="n">
         <v>249.6265501086548</v>
@@ -38158,7 +38158,7 @@
         <v>356.4570219027464</v>
       </c>
       <c r="P45" t="n">
-        <v>113.6660045146532</v>
+        <v>228.6660045146532</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
